--- a/jobs_tracker.xlsx
+++ b/jobs_tracker.xlsx
@@ -37,15 +37,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color rgb="FF0000FF"/>
+      <u val="single"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <color rgb="FF0000FF"/>
-      <u val="single"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -190,39 +190,39 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1001"/>
+  <dimension ref="A1:Z1007"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="11.88" customWidth="1" style="27" min="1" max="1"/>
@@ -690,47 +690,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Experience</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Tech</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>Job URL</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Applied</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>Recruiter</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Employee Contacted</t>
         </is>
@@ -1367,12 +1367,32 @@
       <c r="Z14" s="16" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n"/>
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="22" t="n"/>
-      <c r="D15" s="22" t="n"/>
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Marketwatch</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
       <c r="E15" s="22" t="n"/>
-      <c r="F15" s="22" t="n"/>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>https://www.marketwatch.com/investing/index/mid</t>
+        </is>
+      </c>
       <c r="G15" s="24" t="n"/>
       <c r="H15" s="22" t="n"/>
       <c r="I15" s="22" t="n"/>
@@ -28977,12 +28997,12 @@
     <row r="1001">
       <c r="A1001" s="28" t="inlineStr">
         <is>
-          <t>Marketwatch</t>
+          <t>Synechron</t>
         </is>
       </c>
       <c r="B1001" s="28" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Other TechnologiesStaff Data EngineerSydney</t>
         </is>
       </c>
       <c r="C1001" s="28" t="inlineStr">
@@ -29002,6 +29022,180 @@
         </is>
       </c>
       <c r="H1001" s="28" t="inlineStr"/>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="28" t="inlineStr">
+        <is>
+          <t>Roadmap</t>
+        </is>
+      </c>
+      <c r="B1002" s="28" t="inlineStr">
+        <is>
+          <t>Backend Developer Roadmap: What is Backend Development</t>
+        </is>
+      </c>
+      <c r="C1002" s="28" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D1002" s="28" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="E1002" s="28" t="inlineStr"/>
+      <c r="F1002" s="29" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="H1002" s="28" t="inlineStr"/>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="28" t="inlineStr">
+        <is>
+          <t>Synechron</t>
+        </is>
+      </c>
+      <c r="B1003" s="28" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="C1003" s="28" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="D1003" s="28" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="E1003" s="28" t="inlineStr"/>
+      <c r="F1003" s="29" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="H1003" s="28" t="inlineStr"/>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="28" t="inlineStr">
+        <is>
+          <t>Builtin</t>
+        </is>
+      </c>
+      <c r="B1004" s="28" t="inlineStr">
+        <is>
+          <t>Experienced Software Engineer</t>
+        </is>
+      </c>
+      <c r="C1004" s="28" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D1004" s="28" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="E1004" s="28" t="inlineStr"/>
+      <c r="F1004" s="29" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="H1004" s="28" t="inlineStr"/>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="28" t="inlineStr">
+        <is>
+          <t>Builtin</t>
+        </is>
+      </c>
+      <c r="B1005" s="28" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="C1005" s="28" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D1005" s="28" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="E1005" s="28" t="inlineStr"/>
+      <c r="F1005" s="29" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="H1005" s="28" t="inlineStr"/>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="28" t="inlineStr">
+        <is>
+          <t>Builtin</t>
+        </is>
+      </c>
+      <c r="B1006" s="28" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer II</t>
+        </is>
+      </c>
+      <c r="C1006" s="28" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D1006" s="28" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="E1006" s="28" t="inlineStr"/>
+      <c r="F1006" s="29" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="H1006" s="28" t="inlineStr"/>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="28" t="inlineStr">
+        <is>
+          <t>Ycombinator</t>
+        </is>
+      </c>
+      <c r="B1007" s="28" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="C1007" s="28" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D1007" s="28" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="E1007" s="28" t="inlineStr"/>
+      <c r="F1007" s="29" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="H1007" s="28" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K2:K100">
@@ -29046,11 +29240,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1001" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1001" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1002" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1003" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1004" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1005" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1006" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1007" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId22"/>
   </tableParts>
 </worksheet>
 </file>
@@ -29061,7 +29262,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="51.13" customWidth="1" style="27" min="2" max="2"/>
@@ -29131,7 +29332,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/city/pune-s-fresh-engineering-graduates-face-toughest-job-market-in-years-as-it-companies-slow-entry-level-hiring-article-13939232.html</t>
         </is>
@@ -29141,7 +29342,7 @@
           <t>Role not in target list: 'Pune engineering freshers face toughest job market in years '</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n">
+      <c r="H2" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29166,7 +29367,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>https://www.news18.com/photogallery/business/economy/infosys-starting-salary-for-freshers-in-2026-ai-roles-rs-21-lakh-packages-and-more-ws-l-10224973.html</t>
         </is>
@@ -29176,7 +29377,7 @@
           <t>Role not in target list: 'Infosys Starting Salary For Freshers In 2026: AI Roles, Rs 2'</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n">
+      <c r="H3" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29201,7 +29402,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>https://indianexpress.com/article/education/international-youth-day-fresher-hiring-trends-rises-75-percent-where-young-indians-actually-finding-jobs-top-domains-salary-10829381/</t>
         </is>
@@ -29211,7 +29412,7 @@
           <t>Role not in target list: 'Fresher hiring rises to 75%, but where are young Indians fin'</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n">
+      <c r="H4" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29236,7 +29437,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>https://www.msn.com/en-in/news/other/retail-e-commerce-to-drive-fresher-hiring-in-pune/ar-AA29Ii38</t>
         </is>
@@ -29246,7 +29447,7 @@
           <t>Role not in target list: 'Retail, e-commerce to drive fresher hiring in Pune'</t>
         </is>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="H5" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29271,7 +29472,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>https://timesofindia.indiatimes.com/education/careers/news/fresher-hiring-rises-to-73-in-early-2026-but-the-rules-of-entry-have-changed/articleshow/128504926.cms</t>
         </is>
@@ -29281,7 +29482,7 @@
           <t>Role not in target list: 'Fresher hiring rises to 73% in early 2026, but the rules of '</t>
         </is>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="H6" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29306,7 +29507,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>https://www.analyticsinsight.net/companies/top-tech-companies-hiring-freshers-in-india-the-us-in-2026</t>
         </is>
@@ -29316,7 +29517,7 @@
           <t>Role not in target list: 'Top Tech Companies Hiring Freshers in India, the US in 2026'</t>
         </is>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29341,7 +29542,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>https://www.msn.com/en-in/careers/job-search/ai-gccs-and-a-changing-job-market-india-s-fresher-hiring-is-no-longer-just-an-it-story-who-s-driving-the-shift/ar-AA29wtdN</t>
         </is>
@@ -29351,7 +29552,7 @@
           <t>Role not in target list: 'AI, GCCs and a changing job market: India's fresher hiring i'</t>
         </is>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="H8" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29376,7 +29577,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>https://www.business-standard.com/industry/news/fresher-hiring-gains-in-manufacturing-retail-as-it-demand-cools-report-126081001534_1.html</t>
         </is>
@@ -29386,7 +29587,7 @@
           <t>Role not in target list: 'Fresher hiring gains in manufacturing, retail as IT demand c'</t>
         </is>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29411,7 +29612,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>https://www.careerindia.com/tips/india-hiring-surge-2026-best-ai-non-it-jobs-career-guide-011-65453.html</t>
         </is>
@@ -29421,7 +29622,7 @@
           <t>Role not in target list: 'August Hiring Surge: Top AI and Non-IT Jobs for Freshers to '</t>
         </is>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="H10" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29446,7 +29647,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>https://www.mayoclinic.org/healthy-lifestyle/fitness/in-depth/walking/art-20046261</t>
         </is>
@@ -29456,7 +29657,7 @@
           <t>Role not in target list: 'Walking: Trim your waistline, improve your health'</t>
         </is>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29481,7 +29682,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Bengaluru---Thanissandra-BCIT/Tech-Chapter-Lead---Python--AWS--LLM-Engineering---Microservices_JR1044126</t>
         </is>
@@ -29491,7 +29692,7 @@
           <t>Role not in target list: 'Other TechnologiesTech Chapter Lead'</t>
         </is>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29516,7 +29717,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>https://www.bigbinary.com/careers/ruby-on-rails-engineer</t>
         </is>
@@ -29526,7 +29727,7 @@
           <t>Role not in target list: 'Ruby on Rails Engineer&gt;RemoteCurrently not hiring'</t>
         </is>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29551,7 +29752,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>https://www.bigbinary.com/careers/react-native-engineer</t>
         </is>
@@ -29561,7 +29762,7 @@
           <t>Role not in target list: 'React Native Engineer&gt;RemoteCurrently not hiring'</t>
         </is>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="H14" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29586,7 +29787,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>https://www.bigbinary.com/careers/react-js-engineer</t>
         </is>
@@ -29596,7 +29797,7 @@
           <t>Role not in target list: 'ReactJS Engineer&gt;RemoteCurrently not hiring'</t>
         </is>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29621,7 +29822,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>https://www.bigbinary.com/careers/ui-engineer</t>
         </is>
@@ -29631,7 +29832,7 @@
           <t>Role not in target list: 'Frontend UI Engineer&gt;RemoteCurrently not hiring'</t>
         </is>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="H16" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29656,7 +29857,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>https://dictionary.cambridge.org/dictionary/english/fresher</t>
         </is>
@@ -29666,7 +29867,7 @@
           <t>Role not in target list: 'FRESHER'</t>
         </is>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="H17" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29691,7 +29892,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>https://www.merriam-webster.com/dictionary/fresher</t>
         </is>
@@ -29701,7 +29902,7 @@
           <t>Role not in target list: 'FRESHER Definition &amp; Meaning'</t>
         </is>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="H18" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29726,7 +29927,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>https://www.freshersworld.com/</t>
         </is>
@@ -29736,7 +29937,7 @@
           <t>Role not in target list: 'Freshers Job Vacancies in India'</t>
         </is>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="H19" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29762,7 +29963,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>https://www.persistent.com/services/software-product-engineering/</t>
         </is>
@@ -29773,7 +29974,7 @@
                         Engineering'</t>
         </is>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="H20" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29799,7 +30000,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>https://marketplace.persistentproducts.com/marketplace/#/storefront/taxonomy?categoryId=31&amp;level1Name=IOT&amp;level2Name=</t>
         </is>
@@ -29810,7 +30011,7 @@
     (IoT)'</t>
         </is>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="H21" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29835,7 +30036,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>https://www.kpit.com/expertise/virtual-engineering/</t>
         </is>
@@ -29845,7 +30046,7 @@
           <t>Role not in target list: 'Virtual Engineering'</t>
         </is>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="H22" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29870,7 +30071,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>https://www.kpit.com/expertise/vehicle-engineering-and-design/</t>
         </is>
@@ -29880,7 +30081,7 @@
           <t>Role not in target list: 'Vehicle Engineering &amp; Design'</t>
         </is>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="H23" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29905,7 +30106,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>https://www.forbes.com/lists/best-employers-for-engineers/</t>
         </is>
@@ -29915,7 +30116,7 @@
           <t>Role not in target list: 'Forbes Best Employers for EngineersEmerson is proud to be a '</t>
         </is>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="H24" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29940,7 +30141,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>https://www.emerson.com/en/corporate/careers/military</t>
         </is>
@@ -29950,7 +30151,7 @@
           <t>Role not in target list: 'Veteran Careers and Transition Assistance ProgramsHiring ded'</t>
         </is>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="H25" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29975,7 +30176,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Bengaluru---Bellandur-GTP/Platform-Support-Engineer_JR1044543-1</t>
         </is>
@@ -29985,7 +30186,7 @@
           <t>Role not in target list: 'Other TechnologiesPlatform Support EngineerBengaluru'</t>
         </is>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="H26" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30010,7 +30211,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Bengaluru---Bellandur-GTP/Job-Title--Android-Engineer_JR1044604-1</t>
         </is>
@@ -30020,7 +30221,7 @@
           <t>Role not in target list: 'MobileJob Title: Android EngineerBengaluru'</t>
         </is>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="H27" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30045,7 +30246,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Novi-Sad/AI-Architect_JR1044260-1</t>
         </is>
@@ -30055,7 +30256,7 @@
           <t>Role not in target list: 'AI/ML/Data ScienceSolution Architect (AI oriented)Novi Sad, '</t>
         </is>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="H28" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30080,7 +30281,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Belgrade/AI-Architect_JR1044256</t>
         </is>
@@ -30090,7 +30291,7 @@
           <t>Role not in target list: 'AI/ML/Data ScienceSolution Architect (AI oriented)Belgrade, '</t>
         </is>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="H29" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30115,7 +30316,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>https://www.bmc.com/it-solutions/bmc-ami-devx.html</t>
         </is>
@@ -30125,7 +30326,7 @@
           <t>Role not in target list: 'BMC AMI DevXEmpower next-gen developers with a mainframe-inc'</t>
         </is>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="H30" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30150,7 +30351,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>https://pubmatic.com/solutions/mobile/</t>
         </is>
@@ -30160,7 +30361,7 @@
           <t>Role not in target list: 'FOR APP DEVELOPERS'</t>
         </is>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="H31" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30185,7 +30386,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>https://pubmatic.com/careers/engineering/</t>
         </is>
@@ -30195,7 +30396,7 @@
           <t>Role not in target list: 'Engineering'</t>
         </is>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="H32" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30220,7 +30421,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>https://pubmatic.com/careers/engineering</t>
         </is>
@@ -30230,7 +30431,7 @@
           <t>Role not in target list: 'Engineering'</t>
         </is>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="H33" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30255,7 +30456,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>https://search.jobs.barclays/early-careers</t>
         </is>
@@ -30265,7 +30466,7 @@
           <t>Role not in target list: 'Graduates and internsOur graduate programmes and internships'</t>
         </is>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="H34" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30290,7 +30491,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>https://www.phonepe.com/careers/job-openings/?department=engineering</t>
         </is>
@@ -30300,7 +30501,7 @@
           <t>Role not in target list: 'Engineering'</t>
         </is>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="H35" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30325,7 +30526,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F36" s="12" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>https://go.acceldata.io/isg-buyers-guide-data-quality-data-observability-2026</t>
         </is>
@@ -30335,7 +30536,7 @@
           <t>Role not in target list: 'Acceldata recognized as an Exemplary Leader in 2026 ISG Buye'</t>
         </is>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="H36" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30360,7 +30561,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>https://www.acceldata.io/platform</t>
         </is>
@@ -30370,7 +30571,7 @@
           <t>Role not in target list: 'xLake ArchitectureBuild and run intelligent data and AI pipe'</t>
         </is>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="H37" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30395,7 +30596,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>https://www.e-zest.com/digital-product-engineering-services</t>
         </is>
@@ -30405,7 +30606,7 @@
           <t>Role not in target list: 'Product Engineering'</t>
         </is>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="H38" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30430,7 +30631,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>https://www.e-zest.com/engineering-lead</t>
         </is>
@@ -30440,7 +30641,7 @@
           <t>Role not in target list: 'Engineering Lead'</t>
         </is>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="H39" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30465,7 +30666,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F40" s="12" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>https://www.e-zest.com/sr-kafka-engineer</t>
         </is>
@@ -30475,7 +30676,7 @@
           <t>Role not in target list: 'Sr. Kafka Engineer'</t>
         </is>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="H40" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30500,7 +30701,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>https://www.e-zest.com/sr-node-developer</t>
         </is>
@@ -30510,7 +30711,7 @@
           <t>Role not in target list: 'Sr. Node Developer'</t>
         </is>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="H41" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30535,7 +30736,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F42" s="12" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>https://www.e-zest.com/sr-react-developer</t>
         </is>
@@ -30545,7 +30746,7 @@
           <t>Role not in target list: 'Sr. React Developer'</t>
         </is>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="H42" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30570,7 +30771,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>https://www.e-zest.com/sr-automation-test-engineer</t>
         </is>
@@ -30580,7 +30781,7 @@
           <t>Role not in target list: 'Sr. Automation Test Engineer'</t>
         </is>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="H43" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30605,7 +30806,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F44" s="12" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>https://dbs.wd3.myworkdayjobs.com/DBS_Careers</t>
         </is>
@@ -30615,7 +30816,7 @@
           <t>Role not in target list: 'International Centres'</t>
         </is>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="H44" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30640,7 +30841,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>https://www.dbs.com/careers/internships/default.page</t>
         </is>
@@ -30650,7 +30851,7 @@
           <t>Role not in target list: 'Internships'</t>
         </is>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="H45" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30675,7 +30876,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F46" s="12" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>https://khoros.ai/developer/</t>
         </is>
@@ -30685,7 +30886,7 @@
           <t>Role not in target list: 'Developer Portal'</t>
         </is>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="H46" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30710,7 +30911,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F47" s="12" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>https://razorpay.com/accept-international-payments/</t>
         </is>
@@ -30720,7 +30921,7 @@
           <t>Role not in target list: 'International Payments'</t>
         </is>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="H47" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30745,7 +30946,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F48" s="12" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>https://razorpay.com/docs/</t>
         </is>
@@ -30755,7 +30956,7 @@
           <t>Role not in target list: 'Developer Docs'</t>
         </is>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="H48" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30780,7 +30981,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F49" s="12" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>https://razorpay.com/careers/#ai-builders</t>
         </is>
@@ -30790,7 +30991,7 @@
           <t>Role not in target list: 'HiringAI Builders'</t>
         </is>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="H49" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30815,7 +31016,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F50" s="12" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>https://razorpay.com/ai-builders/</t>
         </is>
@@ -30825,7 +31026,7 @@
           <t>Role not in target list: 'Hiring the MostObsessed AI BuildersHiring the MostObsessed A'</t>
         </is>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="H50" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30850,7 +31051,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F51" s="12" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>https://www.atlassian.com/company/careers/all-jobs?team=Engineering%2CIT%2CSecurity%2CSite%20Reliability%20Engineering&amp;location=&amp;search=</t>
         </is>
@@ -30860,7 +31061,7 @@
           <t>Role not in target list: 'Engineering'</t>
         </is>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="H51" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30885,7 +31086,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F52" s="12" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>https://www.atlassian.com/company/careers/all-jobs?team=Engineering&amp;location=&amp;search=</t>
         </is>
@@ -30895,7 +31096,7 @@
           <t>Role not in target list: 'Browse all engineering roles'</t>
         </is>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="H52" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30920,7 +31121,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F53" s="12" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>https://www.atlassian.com/company/careers/earlycareers</t>
         </is>
@@ -30930,7 +31131,7 @@
           <t>Role not in target list: 'student and internship opportunities'</t>
         </is>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="H53" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30955,7 +31156,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F54" s="12" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>https://www.moengage.com/role/for-developers/</t>
         </is>
@@ -30965,7 +31166,7 @@
           <t>Role not in target list: 'For Developers'</t>
         </is>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="H54" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30990,7 +31191,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F55" s="12" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>https://www.moengage.com/docs/developer-guide/introduction</t>
         </is>
@@ -31000,7 +31201,7 @@
           <t>Role not in target list: 'Developer Hub'</t>
         </is>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="H55" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31025,7 +31226,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F56" s="12" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>https://www.emerson.com/en/corporate/about-us/living-our-purpose</t>
         </is>
@@ -31035,7 +31236,7 @@
           <t>Role not in target list: 'Living Our PurposeWe drive innovation that makes the world h'</t>
         </is>
       </c>
-      <c r="H56" s="13" t="n">
+      <c r="H56" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31060,7 +31261,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F57" s="12" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>https://www.acceldata.io/capabilities/ai-pipelines</t>
         </is>
@@ -31070,7 +31271,7 @@
           <t>Role not in target list: 'AI PipelinesDesign and run autonomous HITL workflows orchest'</t>
         </is>
       </c>
-      <c r="H57" s="13" t="n">
+      <c r="H57" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31095,7 +31296,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F58" s="12" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>https://www.zenoti.com/platform/ai-lead-management</t>
         </is>
@@ -31105,7 +31306,7 @@
           <t>Role not in target list: 'AI Lead Management'</t>
         </is>
       </c>
-      <c r="H58" s="13" t="n">
+      <c r="H58" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31130,7 +31331,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F59" s="12" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>https://leena.ai/agentic-ai-architecture</t>
         </is>
@@ -31140,7 +31341,7 @@
           <t>Role not in target list: 'Agentic AI Architecture Overview'</t>
         </is>
       </c>
-      <c r="H59" s="13" t="n">
+      <c r="H59" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31165,7 +31366,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F60" s="12" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>https://atlan.com/careers/#job-list</t>
         </is>
@@ -31175,7 +31376,2216 @@
           <t>Role not in target list: 'See roles that match these traits'</t>
         </is>
       </c>
-      <c r="H60" s="13" t="n">
+      <c r="H60" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>Moneycontrol</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pune engineering freshers face toughest job market in years </t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/city/pune-s-fresh-engineering-graduates-face-toughest-job-market-in-years-as-it-companies-slow-entry-level-hiring-article-13939232.html</t>
+        </is>
+      </c>
+      <c r="G61" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Pune engineering freshers face toughest job market in years '</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>News18</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t>Infosys Starting Salary For Freshers In 2026: AI Roles, Rs 2</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>https://www.news18.com/photogallery/business/economy/infosys-starting-salary-for-freshers-in-2026-ai-roles-rs-21-lakh-packages-and-more-ws-l-10224973.html</t>
+        </is>
+      </c>
+      <c r="G62" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Infosys Starting Salary For Freshers In 2026: AI Roles, Rs 2'</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>Indianexpress</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>Fresher hiring rises to 75%, but where are young Indians fin</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/education/international-youth-day-fresher-hiring-trends-rises-75-percent-where-young-indians-actually-finding-jobs-top-domains-salary-10829381/</t>
+        </is>
+      </c>
+      <c r="G63" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Fresher hiring rises to 75%, but where are young Indians fin'</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>Timesofindia</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>Retail, e-commerce to drive fresher hiring in Pune</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/retail-e-commerce-to-drive-fresher-hiring-in-pune/articleshow/133074078.cms</t>
+        </is>
+      </c>
+      <c r="G64" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Retail, e-commerce to drive fresher hiring in Pune'</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>Timesofindia</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fresher hiring rises to 73% in early 2026, but the rules of </t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/education/careers/news/fresher-hiring-rises-to-73-in-early-2026-but-the-rules-of-entry-have-changed/articleshow/128504926.cms</t>
+        </is>
+      </c>
+      <c r="G65" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Fresher hiring rises to 73% in early 2026, but the rules of '</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>Fresher hiring gains in manufacturing, retail as IT demand c</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/industry/news/fresher-hiring-gains-in-manufacturing-retail-as-it-demand-cools-report-126081001534_1.html</t>
+        </is>
+      </c>
+      <c r="G66" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Fresher hiring gains in manufacturing, retail as IT demand c'</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>Msn</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>AI, GCCs and a changing job market: India's fresher hiring i</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/careers/job-search/ai-gccs-and-a-changing-job-market-india-s-fresher-hiring-is-no-longer-just-an-it-story-who-s-driving-the-shift/ar-AA29wtdN</t>
+        </is>
+      </c>
+      <c r="G67" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'AI, GCCs and a changing job market: India's fresher hiring i'</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>Careerindia</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">August Hiring Surge: Top AI and Non-IT Jobs for Freshers to </t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D68" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>https://www.careerindia.com/tips/india-hiring-surge-2026-best-ai-non-it-jobs-career-guide-011-65453.html</t>
+        </is>
+      </c>
+      <c r="G68" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'August Hiring Surge: Top AI and Non-IT Jobs for Freshers to '</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>Newindianexpress</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>Indian IT companies raise fresher salaries for elite AI role</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>https://www.newindianexpress.com/business/2026/Jan/13/indian-it-companies-raise-fresher-salaries-for-elite-ai-roles-2</t>
+        </is>
+      </c>
+      <c r="G69" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Indian IT companies raise fresher salaries for elite AI role'</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>Unstop</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>Internships in India 2026: 914+ Verified Internships</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>https://unstop.com/internship</t>
+        </is>
+      </c>
+      <c r="G70" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Internships in India 2026: 914+ Verified Internships'</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>Mayoclinic</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>Walking: Trim your waistline, improve your health</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D71" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mayoclinic.org/healthy-lifestyle/fitness/in-depth/walking/art-20046261</t>
+        </is>
+      </c>
+      <c r="G71" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Walking: Trim your waistline, improve your health'</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>BigBinary</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>Ruby on Rails Engineer&gt;RemoteCurrently not hiring</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D72" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bigbinary.com/careers/ruby-on-rails-engineer</t>
+        </is>
+      </c>
+      <c r="G72" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Ruby on Rails Engineer&gt;RemoteCurrently not hiring'</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>BigBinary</t>
+        </is>
+      </c>
+      <c r="B73" s="1" t="inlineStr">
+        <is>
+          <t>React Native Engineer&gt;RemoteCurrently not hiring</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bigbinary.com/careers/react-native-engineer</t>
+        </is>
+      </c>
+      <c r="G73" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'React Native Engineer&gt;RemoteCurrently not hiring'</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>BigBinary</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>ReactJS Engineer&gt;RemoteCurrently not hiring</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bigbinary.com/careers/react-js-engineer</t>
+        </is>
+      </c>
+      <c r="G74" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'ReactJS Engineer&gt;RemoteCurrently not hiring'</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>BigBinary</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t>Frontend UI Engineer&gt;RemoteCurrently not hiring</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bigbinary.com/careers/ui-engineer</t>
+        </is>
+      </c>
+      <c r="G75" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Frontend UI Engineer&gt;RemoteCurrently not hiring'</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t>eBay Developers Program</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>https://community.ebay.com/forum/ebay-developers-program-57950/</t>
+        </is>
+      </c>
+      <c r="G76" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'eBay Developers Program'</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>Walkin</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>Walk In Counseling</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>https://walkin.org/</t>
+        </is>
+      </c>
+      <c r="G77" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Walk In Counseling'</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>Persistent Systems</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>Software Product
+                        Engineering</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>https://www.persistent.com/services/software-product-engineering/</t>
+        </is>
+      </c>
+      <c r="G78" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Software Product
+                        Engineering'</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>Persistent Systems</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>Internet of Things
+    (IoT)</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>https://marketplace.persistentproducts.com/marketplace/#/storefront/taxonomy?categoryId=31&amp;level1Name=IOT&amp;level2Name=</t>
+        </is>
+      </c>
+      <c r="G79" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Internet of Things
+    (IoT)'</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>KPIT Technologies</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>Virtual Engineering</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kpit.com/expertise/virtual-engineering/</t>
+        </is>
+      </c>
+      <c r="G80" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Virtual Engineering'</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>KPIT Technologies</t>
+        </is>
+      </c>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>Vehicle Engineering &amp; Design</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kpit.com/expertise/vehicle-engineering-and-design/</t>
+        </is>
+      </c>
+      <c r="G81" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Vehicle Engineering &amp; Design'</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forbes Best Employers for EngineersEmerson is proud to be a </t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>https://www.forbes.com/lists/best-employers-for-engineers/</t>
+        </is>
+      </c>
+      <c r="G82" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Forbes Best Employers for EngineersEmerson is proud to be a '</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>Veteran Careers and Transition Assistance ProgramsHiring ded</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>https://www.emerson.com/en/corporate/careers/military</t>
+        </is>
+      </c>
+      <c r="G83" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Veteran Careers and Transition Assistance ProgramsHiring ded'</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>Synechron</t>
+        </is>
+      </c>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t>NodeFull Stack Engineer  (Node + React)Bengaluru</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Bengaluru---Bellandur-GTP/Full-Stack-Engineer---Node---React-_JR1044648-1</t>
+        </is>
+      </c>
+      <c r="G84" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'NodeFull Stack Engineer  (Node + React)Bengaluru'</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>Synechron</t>
+        </is>
+      </c>
+      <c r="B85" s="1" t="inlineStr">
+        <is>
+          <t>NodeFull Stack Engineer  (Node + React)Bengaluru</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Bengaluru---Bellandur-GTP/Full-Stack-Engineer---Node---React-_JR1044647-1</t>
+        </is>
+      </c>
+      <c r="G85" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'NodeFull Stack Engineer  (Node + React)Bengaluru'</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>Synechron</t>
+        </is>
+      </c>
+      <c r="B86" s="1" t="inlineStr">
+        <is>
+          <t>Other TechnologiesPlatform Support EngineerBengaluru</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Bengaluru---Bellandur-GTP/Platform-Support-Engineer_JR1044543-1</t>
+        </is>
+      </c>
+      <c r="G86" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Other TechnologiesPlatform Support EngineerBengaluru'</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>Synechron</t>
+        </is>
+      </c>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
+          <t>MobileJob Title: Android EngineerBengaluru</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Bengaluru---Bellandur-GTP/Job-Title--Android-Engineer_JR1044604-1</t>
+        </is>
+      </c>
+      <c r="G87" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'MobileJob Title: Android EngineerBengaluru'</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>Synechron</t>
+        </is>
+      </c>
+      <c r="B88" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/ML/Data ScienceSolution Architect (AI oriented)Novi Sad, </t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Novi-Sad/AI-Architect_JR1044260-1</t>
+        </is>
+      </c>
+      <c r="G88" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'AI/ML/Data ScienceSolution Architect (AI oriented)Novi Sad, '</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>Synechron</t>
+        </is>
+      </c>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/ML/Data ScienceSolution Architect (AI oriented)Belgrade, </t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Belgrade/AI-Architect_JR1044256</t>
+        </is>
+      </c>
+      <c r="G89" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'AI/ML/Data ScienceSolution Architect (AI oriented)Belgrade, '</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>BMC Software</t>
+        </is>
+      </c>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>BMC AMI DevXEmpower next-gen developers with a mainframe-inc</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bmc.com/it-solutions/bmc-ami-devx.html</t>
+        </is>
+      </c>
+      <c r="G90" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'BMC AMI DevXEmpower next-gen developers with a mainframe-inc'</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>Pubmatic</t>
+        </is>
+      </c>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t>FOR APP DEVELOPERS</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D91" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>https://pubmatic.com/solutions/mobile/</t>
+        </is>
+      </c>
+      <c r="G91" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'FOR APP DEVELOPERS'</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>Pubmatic</t>
+        </is>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>https://pubmatic.com/careers/engineering/</t>
+        </is>
+      </c>
+      <c r="G92" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Engineering'</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>Pubmatic</t>
+        </is>
+      </c>
+      <c r="B93" s="1" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>https://pubmatic.com/careers/engineering</t>
+        </is>
+      </c>
+      <c r="G93" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Engineering'</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>Barclays</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>Graduates and internsOur graduate programmes and internships</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D94" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>https://search.jobs.barclays/early-careers</t>
+        </is>
+      </c>
+      <c r="G94" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Graduates and internsOur graduate programmes and internships'</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>PhonePe</t>
+        </is>
+      </c>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phonepe.com/careers/job-openings/?department=engineering</t>
+        </is>
+      </c>
+      <c r="G95" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Engineering'</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>MiQ</t>
+        </is>
+      </c>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t>Sales Engineering</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>https://www.wearemiq.com/careers?departments=sales-engineering</t>
+        </is>
+      </c>
+      <c r="G96" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Sales Engineering'</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>Acceldata</t>
+        </is>
+      </c>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t>Acceldata recognized as an Exemplary Leader in 2026 ISG Buye</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D97" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>https://go.acceldata.io/isg-buyers-guide-data-quality-data-observability-2026</t>
+        </is>
+      </c>
+      <c r="G97" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Acceldata recognized as an Exemplary Leader in 2026 ISG Buye'</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>Acceldata</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>xLake ArchitectureBuild and run intelligent data and AI pipe</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>https://www.acceldata.io/platform</t>
+        </is>
+      </c>
+      <c r="G98" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'xLake ArchitectureBuild and run intelligent data and AI pipe'</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>e-Zest Solutions</t>
+        </is>
+      </c>
+      <c r="B99" s="1" t="inlineStr">
+        <is>
+          <t>Product Engineering</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D99" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>https://www.e-zest.com/digital-product-engineering-services</t>
+        </is>
+      </c>
+      <c r="G99" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Product Engineering'</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>e-Zest Solutions</t>
+        </is>
+      </c>
+      <c r="B100" s="1" t="inlineStr">
+        <is>
+          <t>Engineering Lead</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D100" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>https://www.e-zest.com/engineering-lead</t>
+        </is>
+      </c>
+      <c r="G100" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Engineering Lead'</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>e-Zest Solutions</t>
+        </is>
+      </c>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>Sr. Kafka Engineer</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D101" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>https://www.e-zest.com/sr-kafka-engineer</t>
+        </is>
+      </c>
+      <c r="G101" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Sr. Kafka Engineer'</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>e-Zest Solutions</t>
+        </is>
+      </c>
+      <c r="B102" s="1" t="inlineStr">
+        <is>
+          <t>Sr. Node Developer</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>https://www.e-zest.com/sr-node-developer</t>
+        </is>
+      </c>
+      <c r="G102" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Sr. Node Developer'</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>e-Zest Solutions</t>
+        </is>
+      </c>
+      <c r="B103" s="1" t="inlineStr">
+        <is>
+          <t>Sr. React Developer</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D103" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>https://www.e-zest.com/sr-react-developer</t>
+        </is>
+      </c>
+      <c r="G103" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Sr. React Developer'</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>e-Zest Solutions</t>
+        </is>
+      </c>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>Sr. Automation Test Engineer</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>https://www.e-zest.com/sr-automation-test-engineer</t>
+        </is>
+      </c>
+      <c r="G104" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Sr. Automation Test Engineer'</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>DBS Bank</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>International Centres</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>https://dbs.wd3.myworkdayjobs.com/DBS_Careers</t>
+        </is>
+      </c>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'International Centres'</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>DBS Bank</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t>Internships</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D106" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>https://www.dbs.com/careers/internships/default.page</t>
+        </is>
+      </c>
+      <c r="G106" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Internships'</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>Khoros</t>
+        </is>
+      </c>
+      <c r="B107" s="1" t="inlineStr">
+        <is>
+          <t>Developer Portal</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D107" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>https://khoros.ai/developer/</t>
+        </is>
+      </c>
+      <c r="G107" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Developer Portal'</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>Razorpay</t>
+        </is>
+      </c>
+      <c r="B108" s="1" t="inlineStr">
+        <is>
+          <t>International Payments</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>https://razorpay.com/accept-international-payments/</t>
+        </is>
+      </c>
+      <c r="G108" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'International Payments'</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>Razorpay</t>
+        </is>
+      </c>
+      <c r="B109" s="1" t="inlineStr">
+        <is>
+          <t>Developer Docs</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D109" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>https://razorpay.com/docs/</t>
+        </is>
+      </c>
+      <c r="G109" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Developer Docs'</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>Razorpay</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="inlineStr">
+        <is>
+          <t>HiringAI Builders</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>https://razorpay.com/careers/#ai-builders</t>
+        </is>
+      </c>
+      <c r="G110" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'HiringAI Builders'</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>Razorpay</t>
+        </is>
+      </c>
+      <c r="B111" s="1" t="inlineStr">
+        <is>
+          <t>Hiring the MostObsessed AI BuildersHiring the MostObsessed A</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D111" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>https://razorpay.com/ai-builders/</t>
+        </is>
+      </c>
+      <c r="G111" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Hiring the MostObsessed AI BuildersHiring the MostObsessed A'</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D112" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/all-jobs?team=Engineering%2CIT%2CSecurity%2CSite%20Reliability%20Engineering&amp;location=&amp;search=</t>
+        </is>
+      </c>
+      <c r="G112" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Engineering'</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="inlineStr">
+        <is>
+          <t>Browse all engineering roles</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D113" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/all-jobs?team=Engineering&amp;location=&amp;search=</t>
+        </is>
+      </c>
+      <c r="G113" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Browse all engineering roles'</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="B114" s="1" t="inlineStr">
+        <is>
+          <t>student and internship opportunities</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D114" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/earlycareers</t>
+        </is>
+      </c>
+      <c r="G114" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'student and internship opportunities'</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>CleverTap</t>
+        </is>
+      </c>
+      <c r="B115" s="1" t="inlineStr">
+        <is>
+          <t>User DocumentationUser and Developer Docs for learning Cleve</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D115" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>https://docs.clevertap.com/docs/getting-started</t>
+        </is>
+      </c>
+      <c r="G115" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'User DocumentationUser and Developer Docs for learning Cleve'</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>MoEngage</t>
+        </is>
+      </c>
+      <c r="B116" s="1" t="inlineStr">
+        <is>
+          <t>For Developers</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D116" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>https://www.moengage.com/role/for-developers/</t>
+        </is>
+      </c>
+      <c r="G116" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'For Developers'</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>MoEngage</t>
+        </is>
+      </c>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t>Developer Hub</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D117" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>https://www.moengage.com/docs/developer-guide/introduction</t>
+        </is>
+      </c>
+      <c r="G117" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Developer Hub'</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t>Living Our PurposeWe drive innovation that makes the world h</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D118" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>https://www.emerson.com/en/corporate/about-us/living-our-purpose</t>
+        </is>
+      </c>
+      <c r="G118" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Living Our PurposeWe drive innovation that makes the world h'</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>Acceldata</t>
+        </is>
+      </c>
+      <c r="B119" s="1" t="inlineStr">
+        <is>
+          <t>AI PipelinesDesign and run autonomous HITL workflows orchest</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D119" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>https://www.acceldata.io/capabilities/ai-pipelines</t>
+        </is>
+      </c>
+      <c r="G119" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'AI PipelinesDesign and run autonomous HITL workflows orchest'</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>Zenoti</t>
+        </is>
+      </c>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t>AI Lead Management</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zenoti.com/platform/ai-lead-management</t>
+        </is>
+      </c>
+      <c r="G120" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'AI Lead Management'</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>Leena AI</t>
+        </is>
+      </c>
+      <c r="B121" s="1" t="inlineStr">
+        <is>
+          <t>Agentic AI Architecture Overview</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>https://leena.ai/agentic-ai-architecture</t>
+        </is>
+      </c>
+      <c r="G121" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Agentic AI Architecture Overview'</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>Atlan</t>
+        </is>
+      </c>
+      <c r="B122" s="1" t="inlineStr">
+        <is>
+          <t>See roles that match these traits</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D122" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>https://atlan.com/careers/#job-list</t>
+        </is>
+      </c>
+      <c r="G122" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'See roles that match these traits'</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>CleverTap</t>
+        </is>
+      </c>
+      <c r="B123" s="1" t="inlineStr">
+        <is>
+          <t>See 1:1 AI-Driven Personalization in ActionRequest your Invi</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D123" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>https://clevertap.com/events/cleverai-summit-2026/?utm_source=top-hat-banner&amp;utm_medium=organic&amp;utm_campaign=aisummit-2026-event</t>
+        </is>
+      </c>
+      <c r="G123" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'See 1:1 AI-Driven Personalization in ActionRequest your Invi'</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31240,6 +33650,69 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" location="job-list" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" location="/storefront/taxonomy?categoryId=31&amp;level1Name=IOT&amp;level2Name=" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" location="ai-builders" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" location="job-list" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId122"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs_tracker.xlsx
+++ b/jobs_tracker.xlsx
@@ -37,15 +37,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="FF0000FF"/>
-      <u val="single"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF0000FF"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -190,39 +190,39 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1007"/>
+  <dimension ref="A1:Z1013"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="11.88" customWidth="1" style="27" min="1" max="1"/>
@@ -690,32 +690,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Experience</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Tech</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Job URL</t>
         </is>
@@ -1415,12 +1415,32 @@
       <c r="Z15" s="16" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="22" t="n"/>
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>Synechron</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>Other TechnologiesStaff Data EngineerSydney</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
       <c r="E16" s="22" t="n"/>
-      <c r="F16" s="22" t="n"/>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Sydney---Client-Location/Staff-Data-Engineer_JR1043883-1</t>
+        </is>
+      </c>
       <c r="G16" s="24" t="n"/>
       <c r="H16" s="22" t="n"/>
       <c r="I16" s="22" t="n"/>
@@ -1443,12 +1463,32 @@
       <c r="Z16" s="16" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="n"/>
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="22" t="n"/>
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Roadmap</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>Backend Developer Roadmap: What is Backend Development</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
       <c r="E17" s="22" t="n"/>
-      <c r="F17" s="22" t="n"/>
+      <c r="F17" s="26" t="inlineStr">
+        <is>
+          <t>https://roadmap.sh/backend</t>
+        </is>
+      </c>
       <c r="G17" s="24" t="n"/>
       <c r="H17" s="22" t="n"/>
       <c r="I17" s="22" t="n"/>
@@ -1471,12 +1511,32 @@
       <c r="Z17" s="16" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="22" t="n"/>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="22" t="n"/>
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Synechron</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
       <c r="E18" s="22" t="n"/>
-      <c r="F18" s="22" t="n"/>
+      <c r="F18" s="26" t="inlineStr">
+        <is>
+          <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Bengaluru---Thanissandra-BCIT/Quality-Engineer---PEGA_JR1044533</t>
+        </is>
+      </c>
       <c r="G18" s="24" t="n"/>
       <c r="H18" s="22" t="n"/>
       <c r="I18" s="22" t="n"/>
@@ -1499,12 +1559,32 @@
       <c r="Z18" s="16" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="n"/>
-      <c r="B19" s="22" t="n"/>
-      <c r="C19" s="22" t="n"/>
-      <c r="D19" s="22" t="n"/>
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Builtin</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>Experienced Software Engineer</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
       <c r="E19" s="22" t="n"/>
-      <c r="F19" s="22" t="n"/>
+      <c r="F19" s="26" t="inlineStr">
+        <is>
+          <t>https://builtin.com/job/experienced-software-engineer-java/11367849</t>
+        </is>
+      </c>
       <c r="G19" s="24" t="n"/>
       <c r="H19" s="22" t="n"/>
       <c r="I19" s="22" t="n"/>
@@ -1527,12 +1607,32 @@
       <c r="Z19" s="16" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="n"/>
-      <c r="B20" s="22" t="n"/>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="22" t="n"/>
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Builtin</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
       <c r="E20" s="22" t="n"/>
-      <c r="F20" s="22" t="n"/>
+      <c r="F20" s="26" t="inlineStr">
+        <is>
+          <t>https://builtin.com/job/associate-software-engineer-java/11367841</t>
+        </is>
+      </c>
       <c r="G20" s="24" t="n"/>
       <c r="H20" s="22" t="n"/>
       <c r="I20" s="22" t="n"/>
@@ -1555,12 +1655,32 @@
       <c r="Z20" s="16" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="n"/>
-      <c r="B21" s="22" t="n"/>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="22" t="n"/>
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Builtin</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer II</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
       <c r="E21" s="22" t="n"/>
-      <c r="F21" s="22" t="n"/>
+      <c r="F21" s="26" t="inlineStr">
+        <is>
+          <t>https://builtin.com/job/site-reliability-engineer-ii/11367717</t>
+        </is>
+      </c>
       <c r="G21" s="24" t="n"/>
       <c r="H21" s="22" t="n"/>
       <c r="I21" s="22" t="n"/>
@@ -1583,12 +1703,32 @@
       <c r="Z21" s="16" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="n"/>
-      <c r="B22" s="22" t="n"/>
-      <c r="C22" s="22" t="n"/>
-      <c r="D22" s="22" t="n"/>
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Ycombinator</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
       <c r="E22" s="22" t="n"/>
-      <c r="F22" s="22" t="n"/>
+      <c r="F22" s="26" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/jobs/role/software-engineer</t>
+        </is>
+      </c>
       <c r="G22" s="24" t="n"/>
       <c r="H22" s="22" t="n"/>
       <c r="I22" s="22" t="n"/>
@@ -28997,17 +29137,17 @@
     <row r="1001">
       <c r="A1001" s="28" t="inlineStr">
         <is>
-          <t>Synechron</t>
+          <t>Findmyjobss</t>
         </is>
       </c>
       <c r="B1001" s="28" t="inlineStr">
         <is>
-          <t>Other TechnologiesStaff Data EngineerSydney</t>
+          <t>IQVIA Hiring 2026 For Software Engineer Intern</t>
         </is>
       </c>
       <c r="C1001" s="28" t="inlineStr">
         <is>
-          <t>Pune / Hyderabad / Bangalore</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="D1001" s="28" t="inlineStr">
@@ -29026,17 +29166,17 @@
     <row r="1002">
       <c r="A1002" s="28" t="inlineStr">
         <is>
-          <t>Roadmap</t>
+          <t>Terralogic</t>
         </is>
       </c>
       <c r="B1002" s="28" t="inlineStr">
         <is>
-          <t>Backend Developer Roadmap: What is Backend Development</t>
+          <t>Software Engineering Intern (New Grad Hiring 2026)Posted 1 m</t>
         </is>
       </c>
       <c r="C1002" s="28" t="inlineStr">
         <is>
-          <t>Pune / Hyderabad / Bangalore</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="D1002" s="28" t="inlineStr">
@@ -29055,17 +29195,17 @@
     <row r="1003">
       <c r="A1003" s="28" t="inlineStr">
         <is>
-          <t>Synechron</t>
+          <t>Freshershunt</t>
         </is>
       </c>
       <c r="B1003" s="28" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Fujitsu Software Engineer 2026</t>
         </is>
       </c>
       <c r="C1003" s="28" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="D1003" s="28" t="inlineStr">
@@ -29084,17 +29224,17 @@
     <row r="1004">
       <c r="A1004" s="28" t="inlineStr">
         <is>
-          <t>Builtin</t>
+          <t>Builtinbengaluru</t>
         </is>
       </c>
       <c r="B1004" s="28" t="inlineStr">
         <is>
-          <t>Experienced Software Engineer</t>
+          <t>Software Engineer, Data Platform (Bengaluru)</t>
         </is>
       </c>
       <c r="C1004" s="28" t="inlineStr">
         <is>
-          <t>Pune / Hyderabad / Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="D1004" s="28" t="inlineStr">
@@ -29113,17 +29253,17 @@
     <row r="1005">
       <c r="A1005" s="28" t="inlineStr">
         <is>
-          <t>Builtin</t>
+          <t>Techstartupslist</t>
         </is>
       </c>
       <c r="B1005" s="28" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Applied ML Engineer, Evals &amp; DataCardboard·  Bengalur</t>
         </is>
       </c>
       <c r="C1005" s="28" t="inlineStr">
         <is>
-          <t>Pune / Hyderabad / Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="D1005" s="28" t="inlineStr">
@@ -29142,12 +29282,12 @@
     <row r="1006">
       <c r="A1006" s="28" t="inlineStr">
         <is>
-          <t>Builtin</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="B1006" s="28" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Software Engineering Careers &amp; Job Opportunities</t>
         </is>
       </c>
       <c r="C1006" s="28" t="inlineStr">
@@ -29171,12 +29311,12 @@
     <row r="1007">
       <c r="A1007" s="28" t="inlineStr">
         <is>
-          <t>Ycombinator</t>
+          <t>Topstartups</t>
         </is>
       </c>
       <c r="B1007" s="28" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software EngineerNew</t>
         </is>
       </c>
       <c r="C1007" s="28" t="inlineStr">
@@ -29196,6 +29336,180 @@
         </is>
       </c>
       <c r="H1007" s="28" t="inlineStr"/>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="28" t="inlineStr">
+        <is>
+          <t>Topstartups</t>
+        </is>
+      </c>
+      <c r="B1008" s="28" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer</t>
+        </is>
+      </c>
+      <c r="C1008" s="28" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D1008" s="28" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="E1008" s="28" t="inlineStr"/>
+      <c r="F1008" s="29" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="H1008" s="28" t="inlineStr"/>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="28" t="inlineStr">
+        <is>
+          <t>Topstartups</t>
+        </is>
+      </c>
+      <c r="B1009" s="28" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer, Android</t>
+        </is>
+      </c>
+      <c r="C1009" s="28" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D1009" s="28" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="E1009" s="28" t="inlineStr"/>
+      <c r="F1009" s="29" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="H1009" s="28" t="inlineStr"/>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="28" t="inlineStr">
+        <is>
+          <t>Builtin</t>
+        </is>
+      </c>
+      <c r="B1010" s="28" t="inlineStr">
+        <is>
+          <t>Embedded Linux Platform Engineer</t>
+        </is>
+      </c>
+      <c r="C1010" s="28" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D1010" s="28" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="E1010" s="28" t="inlineStr"/>
+      <c r="F1010" s="29" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="H1010" s="28" t="inlineStr"/>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="28" t="inlineStr">
+        <is>
+          <t>Builtin</t>
+        </is>
+      </c>
+      <c r="B1011" s="28" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="C1011" s="28" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D1011" s="28" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="E1011" s="28" t="inlineStr"/>
+      <c r="F1011" s="29" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="H1011" s="28" t="inlineStr"/>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="28" t="inlineStr">
+        <is>
+          <t>Techstartupslist</t>
+        </is>
+      </c>
+      <c r="B1012" s="28" t="inlineStr">
+        <is>
+          <t>Software Engineer (Product)Avoca·  Bengaluru, India</t>
+        </is>
+      </c>
+      <c r="C1012" s="28" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="D1012" s="28" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="E1012" s="28" t="inlineStr"/>
+      <c r="F1012" s="29" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="H1012" s="28" t="inlineStr"/>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="28" t="inlineStr">
+        <is>
+          <t>Techstartupslist</t>
+        </is>
+      </c>
+      <c r="B1013" s="28" t="inlineStr">
+        <is>
+          <t>Forward Deployed EngineerNanoNets·  Bengaluru</t>
+        </is>
+      </c>
+      <c r="C1013" s="28" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="D1013" s="28" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="E1013" s="28" t="inlineStr"/>
+      <c r="F1013" s="29" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="H1013" s="28" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K2:K100">
@@ -29241,17 +29555,30 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1001" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1002" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1003" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1004" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1005" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1006" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1007" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1001" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1002" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1003" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1004" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1005" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1006" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1007" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1008" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1009" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1010" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1011" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1012" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1013" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId22"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId35"/>
   </tableParts>
 </worksheet>
 </file>
@@ -29262,7 +29589,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H123"/>
+  <dimension ref="A1:H189"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="51.13" customWidth="1" style="27" min="2" max="2"/>
@@ -29332,7 +29659,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/city/pune-s-fresh-engineering-graduates-face-toughest-job-market-in-years-as-it-companies-slow-entry-level-hiring-article-13939232.html</t>
         </is>
@@ -29342,7 +29669,7 @@
           <t>Role not in target list: 'Pune engineering freshers face toughest job market in years '</t>
         </is>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29367,7 +29694,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>https://www.news18.com/photogallery/business/economy/infosys-starting-salary-for-freshers-in-2026-ai-roles-rs-21-lakh-packages-and-more-ws-l-10224973.html</t>
         </is>
@@ -29377,7 +29704,7 @@
           <t>Role not in target list: 'Infosys Starting Salary For Freshers In 2026: AI Roles, Rs 2'</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29402,7 +29729,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>https://indianexpress.com/article/education/international-youth-day-fresher-hiring-trends-rises-75-percent-where-young-indians-actually-finding-jobs-top-domains-salary-10829381/</t>
         </is>
@@ -29412,7 +29739,7 @@
           <t>Role not in target list: 'Fresher hiring rises to 75%, but where are young Indians fin'</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29437,7 +29764,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>https://www.msn.com/en-in/news/other/retail-e-commerce-to-drive-fresher-hiring-in-pune/ar-AA29Ii38</t>
         </is>
@@ -29447,7 +29774,7 @@
           <t>Role not in target list: 'Retail, e-commerce to drive fresher hiring in Pune'</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29472,7 +29799,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>https://timesofindia.indiatimes.com/education/careers/news/fresher-hiring-rises-to-73-in-early-2026-but-the-rules-of-entry-have-changed/articleshow/128504926.cms</t>
         </is>
@@ -29482,7 +29809,7 @@
           <t>Role not in target list: 'Fresher hiring rises to 73% in early 2026, but the rules of '</t>
         </is>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29507,7 +29834,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>https://www.analyticsinsight.net/companies/top-tech-companies-hiring-freshers-in-india-the-us-in-2026</t>
         </is>
@@ -29517,7 +29844,7 @@
           <t>Role not in target list: 'Top Tech Companies Hiring Freshers in India, the US in 2026'</t>
         </is>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29542,7 +29869,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>https://www.msn.com/en-in/careers/job-search/ai-gccs-and-a-changing-job-market-india-s-fresher-hiring-is-no-longer-just-an-it-story-who-s-driving-the-shift/ar-AA29wtdN</t>
         </is>
@@ -29552,7 +29879,7 @@
           <t>Role not in target list: 'AI, GCCs and a changing job market: India's fresher hiring i'</t>
         </is>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29577,7 +29904,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>https://www.business-standard.com/industry/news/fresher-hiring-gains-in-manufacturing-retail-as-it-demand-cools-report-126081001534_1.html</t>
         </is>
@@ -29587,7 +29914,7 @@
           <t>Role not in target list: 'Fresher hiring gains in manufacturing, retail as IT demand c'</t>
         </is>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29612,7 +29939,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>https://www.careerindia.com/tips/india-hiring-surge-2026-best-ai-non-it-jobs-career-guide-011-65453.html</t>
         </is>
@@ -29622,7 +29949,7 @@
           <t>Role not in target list: 'August Hiring Surge: Top AI and Non-IT Jobs for Freshers to '</t>
         </is>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29647,7 +29974,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>https://www.mayoclinic.org/healthy-lifestyle/fitness/in-depth/walking/art-20046261</t>
         </is>
@@ -29657,7 +29984,7 @@
           <t>Role not in target list: 'Walking: Trim your waistline, improve your health'</t>
         </is>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29682,7 +30009,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Bengaluru---Thanissandra-BCIT/Tech-Chapter-Lead---Python--AWS--LLM-Engineering---Microservices_JR1044126</t>
         </is>
@@ -29692,7 +30019,7 @@
           <t>Role not in target list: 'Other TechnologiesTech Chapter Lead'</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29717,7 +30044,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>https://www.bigbinary.com/careers/ruby-on-rails-engineer</t>
         </is>
@@ -29727,7 +30054,7 @@
           <t>Role not in target list: 'Ruby on Rails Engineer&gt;RemoteCurrently not hiring'</t>
         </is>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29752,7 +30079,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>https://www.bigbinary.com/careers/react-native-engineer</t>
         </is>
@@ -29762,7 +30089,7 @@
           <t>Role not in target list: 'React Native Engineer&gt;RemoteCurrently not hiring'</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29787,7 +30114,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>https://www.bigbinary.com/careers/react-js-engineer</t>
         </is>
@@ -29797,7 +30124,7 @@
           <t>Role not in target list: 'ReactJS Engineer&gt;RemoteCurrently not hiring'</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29822,7 +30149,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>https://www.bigbinary.com/careers/ui-engineer</t>
         </is>
@@ -29832,7 +30159,7 @@
           <t>Role not in target list: 'Frontend UI Engineer&gt;RemoteCurrently not hiring'</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="H16" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29857,7 +30184,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>https://dictionary.cambridge.org/dictionary/english/fresher</t>
         </is>
@@ -29867,7 +30194,7 @@
           <t>Role not in target list: 'FRESHER'</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="H17" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29892,7 +30219,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>https://www.merriam-webster.com/dictionary/fresher</t>
         </is>
@@ -29902,7 +30229,7 @@
           <t>Role not in target list: 'FRESHER Definition &amp; Meaning'</t>
         </is>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="H18" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29927,7 +30254,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>https://www.freshersworld.com/</t>
         </is>
@@ -29937,7 +30264,7 @@
           <t>Role not in target list: 'Freshers Job Vacancies in India'</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="H19" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29963,7 +30290,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>https://www.persistent.com/services/software-product-engineering/</t>
         </is>
@@ -29974,7 +30301,7 @@
                         Engineering'</t>
         </is>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="H20" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30000,7 +30327,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>https://marketplace.persistentproducts.com/marketplace/#/storefront/taxonomy?categoryId=31&amp;level1Name=IOT&amp;level2Name=</t>
         </is>
@@ -30011,7 +30338,7 @@
     (IoT)'</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H21" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30036,7 +30363,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>https://www.kpit.com/expertise/virtual-engineering/</t>
         </is>
@@ -30046,7 +30373,7 @@
           <t>Role not in target list: 'Virtual Engineering'</t>
         </is>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="H22" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30071,7 +30398,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>https://www.kpit.com/expertise/vehicle-engineering-and-design/</t>
         </is>
@@ -30081,7 +30408,7 @@
           <t>Role not in target list: 'Vehicle Engineering &amp; Design'</t>
         </is>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="H23" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30106,7 +30433,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>https://www.forbes.com/lists/best-employers-for-engineers/</t>
         </is>
@@ -30116,7 +30443,7 @@
           <t>Role not in target list: 'Forbes Best Employers for EngineersEmerson is proud to be a '</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n">
+      <c r="H24" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30141,7 +30468,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>https://www.emerson.com/en/corporate/careers/military</t>
         </is>
@@ -30151,7 +30478,7 @@
           <t>Role not in target list: 'Veteran Careers and Transition Assistance ProgramsHiring ded'</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n">
+      <c r="H25" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30176,7 +30503,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Bengaluru---Bellandur-GTP/Platform-Support-Engineer_JR1044543-1</t>
         </is>
@@ -30186,7 +30513,7 @@
           <t>Role not in target list: 'Other TechnologiesPlatform Support EngineerBengaluru'</t>
         </is>
       </c>
-      <c r="H26" s="5" t="n">
+      <c r="H26" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30211,7 +30538,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Bengaluru---Bellandur-GTP/Job-Title--Android-Engineer_JR1044604-1</t>
         </is>
@@ -30221,7 +30548,7 @@
           <t>Role not in target list: 'MobileJob Title: Android EngineerBengaluru'</t>
         </is>
       </c>
-      <c r="H27" s="5" t="n">
+      <c r="H27" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30246,7 +30573,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Novi-Sad/AI-Architect_JR1044260-1</t>
         </is>
@@ -30256,7 +30583,7 @@
           <t>Role not in target list: 'AI/ML/Data ScienceSolution Architect (AI oriented)Novi Sad, '</t>
         </is>
       </c>
-      <c r="H28" s="5" t="n">
+      <c r="H28" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30281,7 +30608,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Belgrade/AI-Architect_JR1044256</t>
         </is>
@@ -30291,7 +30618,7 @@
           <t>Role not in target list: 'AI/ML/Data ScienceSolution Architect (AI oriented)Belgrade, '</t>
         </is>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H29" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30316,7 +30643,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>https://www.bmc.com/it-solutions/bmc-ami-devx.html</t>
         </is>
@@ -30326,7 +30653,7 @@
           <t>Role not in target list: 'BMC AMI DevXEmpower next-gen developers with a mainframe-inc'</t>
         </is>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="H30" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30351,7 +30678,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>https://pubmatic.com/solutions/mobile/</t>
         </is>
@@ -30361,7 +30688,7 @@
           <t>Role not in target list: 'FOR APP DEVELOPERS'</t>
         </is>
       </c>
-      <c r="H31" s="5" t="n">
+      <c r="H31" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30386,7 +30713,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>https://pubmatic.com/careers/engineering/</t>
         </is>
@@ -30396,7 +30723,7 @@
           <t>Role not in target list: 'Engineering'</t>
         </is>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H32" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30421,7 +30748,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>https://pubmatic.com/careers/engineering</t>
         </is>
@@ -30431,7 +30758,7 @@
           <t>Role not in target list: 'Engineering'</t>
         </is>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H33" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30456,7 +30783,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>https://search.jobs.barclays/early-careers</t>
         </is>
@@ -30466,7 +30793,7 @@
           <t>Role not in target list: 'Graduates and internsOur graduate programmes and internships'</t>
         </is>
       </c>
-      <c r="H34" s="5" t="n">
+      <c r="H34" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30491,7 +30818,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t>https://www.phonepe.com/careers/job-openings/?department=engineering</t>
         </is>
@@ -30501,7 +30828,7 @@
           <t>Role not in target list: 'Engineering'</t>
         </is>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="H35" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30526,7 +30853,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>https://go.acceldata.io/isg-buyers-guide-data-quality-data-observability-2026</t>
         </is>
@@ -30536,7 +30863,7 @@
           <t>Role not in target list: 'Acceldata recognized as an Exemplary Leader in 2026 ISG Buye'</t>
         </is>
       </c>
-      <c r="H36" s="5" t="n">
+      <c r="H36" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30561,7 +30888,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>https://www.acceldata.io/platform</t>
         </is>
@@ -30571,7 +30898,7 @@
           <t>Role not in target list: 'xLake ArchitectureBuild and run intelligent data and AI pipe'</t>
         </is>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="H37" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30596,7 +30923,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>https://www.e-zest.com/digital-product-engineering-services</t>
         </is>
@@ -30606,7 +30933,7 @@
           <t>Role not in target list: 'Product Engineering'</t>
         </is>
       </c>
-      <c r="H38" s="5" t="n">
+      <c r="H38" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30631,7 +30958,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>https://www.e-zest.com/engineering-lead</t>
         </is>
@@ -30641,7 +30968,7 @@
           <t>Role not in target list: 'Engineering Lead'</t>
         </is>
       </c>
-      <c r="H39" s="5" t="n">
+      <c r="H39" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30666,7 +30993,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>https://www.e-zest.com/sr-kafka-engineer</t>
         </is>
@@ -30676,7 +31003,7 @@
           <t>Role not in target list: 'Sr. Kafka Engineer'</t>
         </is>
       </c>
-      <c r="H40" s="5" t="n">
+      <c r="H40" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30701,7 +31028,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t>https://www.e-zest.com/sr-node-developer</t>
         </is>
@@ -30711,7 +31038,7 @@
           <t>Role not in target list: 'Sr. Node Developer'</t>
         </is>
       </c>
-      <c r="H41" s="5" t="n">
+      <c r="H41" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30736,7 +31063,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>https://www.e-zest.com/sr-react-developer</t>
         </is>
@@ -30746,7 +31073,7 @@
           <t>Role not in target list: 'Sr. React Developer'</t>
         </is>
       </c>
-      <c r="H42" s="5" t="n">
+      <c r="H42" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30771,7 +31098,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
         <is>
           <t>https://www.e-zest.com/sr-automation-test-engineer</t>
         </is>
@@ -30781,7 +31108,7 @@
           <t>Role not in target list: 'Sr. Automation Test Engineer'</t>
         </is>
       </c>
-      <c r="H43" s="5" t="n">
+      <c r="H43" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30806,7 +31133,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t>https://dbs.wd3.myworkdayjobs.com/DBS_Careers</t>
         </is>
@@ -30816,7 +31143,7 @@
           <t>Role not in target list: 'International Centres'</t>
         </is>
       </c>
-      <c r="H44" s="5" t="n">
+      <c r="H44" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30841,7 +31168,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
         <is>
           <t>https://www.dbs.com/careers/internships/default.page</t>
         </is>
@@ -30851,7 +31178,7 @@
           <t>Role not in target list: 'Internships'</t>
         </is>
       </c>
-      <c r="H45" s="5" t="n">
+      <c r="H45" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30876,7 +31203,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t>https://khoros.ai/developer/</t>
         </is>
@@ -30886,7 +31213,7 @@
           <t>Role not in target list: 'Developer Portal'</t>
         </is>
       </c>
-      <c r="H46" s="5" t="n">
+      <c r="H46" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30911,7 +31238,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F47" s="8" t="inlineStr">
         <is>
           <t>https://razorpay.com/accept-international-payments/</t>
         </is>
@@ -30921,7 +31248,7 @@
           <t>Role not in target list: 'International Payments'</t>
         </is>
       </c>
-      <c r="H47" s="5" t="n">
+      <c r="H47" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30946,7 +31273,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F48" s="8" t="inlineStr">
         <is>
           <t>https://razorpay.com/docs/</t>
         </is>
@@ -30956,7 +31283,7 @@
           <t>Role not in target list: 'Developer Docs'</t>
         </is>
       </c>
-      <c r="H48" s="5" t="n">
+      <c r="H48" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30981,7 +31308,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
         <is>
           <t>https://razorpay.com/careers/#ai-builders</t>
         </is>
@@ -30991,7 +31318,7 @@
           <t>Role not in target list: 'HiringAI Builders'</t>
         </is>
       </c>
-      <c r="H49" s="5" t="n">
+      <c r="H49" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31016,7 +31343,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F50" s="8" t="inlineStr">
         <is>
           <t>https://razorpay.com/ai-builders/</t>
         </is>
@@ -31026,7 +31353,7 @@
           <t>Role not in target list: 'Hiring the MostObsessed AI BuildersHiring the MostObsessed A'</t>
         </is>
       </c>
-      <c r="H50" s="5" t="n">
+      <c r="H50" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31051,7 +31378,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr">
         <is>
           <t>https://www.atlassian.com/company/careers/all-jobs?team=Engineering%2CIT%2CSecurity%2CSite%20Reliability%20Engineering&amp;location=&amp;search=</t>
         </is>
@@ -31061,7 +31388,7 @@
           <t>Role not in target list: 'Engineering'</t>
         </is>
       </c>
-      <c r="H51" s="5" t="n">
+      <c r="H51" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31086,7 +31413,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
         <is>
           <t>https://www.atlassian.com/company/careers/all-jobs?team=Engineering&amp;location=&amp;search=</t>
         </is>
@@ -31096,7 +31423,7 @@
           <t>Role not in target list: 'Browse all engineering roles'</t>
         </is>
       </c>
-      <c r="H52" s="5" t="n">
+      <c r="H52" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31121,7 +31448,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F53" s="8" t="inlineStr">
         <is>
           <t>https://www.atlassian.com/company/careers/earlycareers</t>
         </is>
@@ -31131,7 +31458,7 @@
           <t>Role not in target list: 'student and internship opportunities'</t>
         </is>
       </c>
-      <c r="H53" s="5" t="n">
+      <c r="H53" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31156,7 +31483,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F54" s="8" t="inlineStr">
         <is>
           <t>https://www.moengage.com/role/for-developers/</t>
         </is>
@@ -31166,7 +31493,7 @@
           <t>Role not in target list: 'For Developers'</t>
         </is>
       </c>
-      <c r="H54" s="5" t="n">
+      <c r="H54" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31191,7 +31518,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F55" s="8" t="inlineStr">
         <is>
           <t>https://www.moengage.com/docs/developer-guide/introduction</t>
         </is>
@@ -31201,7 +31528,7 @@
           <t>Role not in target list: 'Developer Hub'</t>
         </is>
       </c>
-      <c r="H55" s="5" t="n">
+      <c r="H55" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31226,7 +31553,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>https://www.emerson.com/en/corporate/about-us/living-our-purpose</t>
         </is>
@@ -31236,7 +31563,7 @@
           <t>Role not in target list: 'Living Our PurposeWe drive innovation that makes the world h'</t>
         </is>
       </c>
-      <c r="H56" s="5" t="n">
+      <c r="H56" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31261,7 +31588,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>https://www.acceldata.io/capabilities/ai-pipelines</t>
         </is>
@@ -31271,7 +31598,7 @@
           <t>Role not in target list: 'AI PipelinesDesign and run autonomous HITL workflows orchest'</t>
         </is>
       </c>
-      <c r="H57" s="5" t="n">
+      <c r="H57" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31296,7 +31623,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
         <is>
           <t>https://www.zenoti.com/platform/ai-lead-management</t>
         </is>
@@ -31306,7 +31633,7 @@
           <t>Role not in target list: 'AI Lead Management'</t>
         </is>
       </c>
-      <c r="H58" s="5" t="n">
+      <c r="H58" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31331,7 +31658,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>https://leena.ai/agentic-ai-architecture</t>
         </is>
@@ -31341,7 +31668,7 @@
           <t>Role not in target list: 'Agentic AI Architecture Overview'</t>
         </is>
       </c>
-      <c r="H59" s="5" t="n">
+      <c r="H59" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31366,7 +31693,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
         <is>
           <t>https://atlan.com/careers/#job-list</t>
         </is>
@@ -31376,7 +31703,7 @@
           <t>Role not in target list: 'See roles that match these traits'</t>
         </is>
       </c>
-      <c r="H60" s="5" t="n">
+      <c r="H60" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31401,7 +31728,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F61" s="8" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/city/pune-s-fresh-engineering-graduates-face-toughest-job-market-in-years-as-it-companies-slow-entry-level-hiring-article-13939232.html</t>
         </is>
@@ -31411,7 +31738,7 @@
           <t>Role not in target list: 'Pune engineering freshers face toughest job market in years '</t>
         </is>
       </c>
-      <c r="H61" s="5" t="n">
+      <c r="H61" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31436,7 +31763,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>https://www.news18.com/photogallery/business/economy/infosys-starting-salary-for-freshers-in-2026-ai-roles-rs-21-lakh-packages-and-more-ws-l-10224973.html</t>
         </is>
@@ -31446,7 +31773,7 @@
           <t>Role not in target list: 'Infosys Starting Salary For Freshers In 2026: AI Roles, Rs 2'</t>
         </is>
       </c>
-      <c r="H62" s="5" t="n">
+      <c r="H62" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31471,7 +31798,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>https://indianexpress.com/article/education/international-youth-day-fresher-hiring-trends-rises-75-percent-where-young-indians-actually-finding-jobs-top-domains-salary-10829381/</t>
         </is>
@@ -31481,7 +31808,7 @@
           <t>Role not in target list: 'Fresher hiring rises to 75%, but where are young Indians fin'</t>
         </is>
       </c>
-      <c r="H63" s="5" t="n">
+      <c r="H63" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31506,7 +31833,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="F64" s="8" t="inlineStr">
         <is>
           <t>https://timesofindia.indiatimes.com/city/pune/retail-e-commerce-to-drive-fresher-hiring-in-pune/articleshow/133074078.cms</t>
         </is>
@@ -31516,7 +31843,7 @@
           <t>Role not in target list: 'Retail, e-commerce to drive fresher hiring in Pune'</t>
         </is>
       </c>
-      <c r="H64" s="5" t="n">
+      <c r="H64" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31541,7 +31868,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="F65" s="8" t="inlineStr">
         <is>
           <t>https://timesofindia.indiatimes.com/education/careers/news/fresher-hiring-rises-to-73-in-early-2026-but-the-rules-of-entry-have-changed/articleshow/128504926.cms</t>
         </is>
@@ -31551,7 +31878,7 @@
           <t>Role not in target list: 'Fresher hiring rises to 73% in early 2026, but the rules of '</t>
         </is>
       </c>
-      <c r="H65" s="5" t="n">
+      <c r="H65" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31576,7 +31903,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr">
+      <c r="F66" s="8" t="inlineStr">
         <is>
           <t>https://www.business-standard.com/industry/news/fresher-hiring-gains-in-manufacturing-retail-as-it-demand-cools-report-126081001534_1.html</t>
         </is>
@@ -31586,7 +31913,7 @@
           <t>Role not in target list: 'Fresher hiring gains in manufacturing, retail as IT demand c'</t>
         </is>
       </c>
-      <c r="H66" s="5" t="n">
+      <c r="H66" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31611,7 +31938,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="F67" s="8" t="inlineStr">
         <is>
           <t>https://www.msn.com/en-in/careers/job-search/ai-gccs-and-a-changing-job-market-india-s-fresher-hiring-is-no-longer-just-an-it-story-who-s-driving-the-shift/ar-AA29wtdN</t>
         </is>
@@ -31621,7 +31948,7 @@
           <t>Role not in target list: 'AI, GCCs and a changing job market: India's fresher hiring i'</t>
         </is>
       </c>
-      <c r="H67" s="5" t="n">
+      <c r="H67" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31646,7 +31973,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="F68" s="8" t="inlineStr">
         <is>
           <t>https://www.careerindia.com/tips/india-hiring-surge-2026-best-ai-non-it-jobs-career-guide-011-65453.html</t>
         </is>
@@ -31656,7 +31983,7 @@
           <t>Role not in target list: 'August Hiring Surge: Top AI and Non-IT Jobs for Freshers to '</t>
         </is>
       </c>
-      <c r="H68" s="5" t="n">
+      <c r="H68" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31681,7 +32008,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F69" s="8" t="inlineStr">
         <is>
           <t>https://www.newindianexpress.com/business/2026/Jan/13/indian-it-companies-raise-fresher-salaries-for-elite-ai-roles-2</t>
         </is>
@@ -31691,7 +32018,7 @@
           <t>Role not in target list: 'Indian IT companies raise fresher salaries for elite AI role'</t>
         </is>
       </c>
-      <c r="H69" s="5" t="n">
+      <c r="H69" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31716,7 +32043,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
+      <c r="F70" s="8" t="inlineStr">
         <is>
           <t>https://unstop.com/internship</t>
         </is>
@@ -31726,7 +32053,7 @@
           <t>Role not in target list: 'Internships in India 2026: 914+ Verified Internships'</t>
         </is>
       </c>
-      <c r="H70" s="5" t="n">
+      <c r="H70" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31751,7 +32078,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F71" s="8" t="inlineStr">
         <is>
           <t>https://www.mayoclinic.org/healthy-lifestyle/fitness/in-depth/walking/art-20046261</t>
         </is>
@@ -31761,7 +32088,7 @@
           <t>Role not in target list: 'Walking: Trim your waistline, improve your health'</t>
         </is>
       </c>
-      <c r="H71" s="5" t="n">
+      <c r="H71" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31786,7 +32113,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="F72" s="8" t="inlineStr">
         <is>
           <t>https://www.bigbinary.com/careers/ruby-on-rails-engineer</t>
         </is>
@@ -31796,7 +32123,7 @@
           <t>Role not in target list: 'Ruby on Rails Engineer&gt;RemoteCurrently not hiring'</t>
         </is>
       </c>
-      <c r="H72" s="5" t="n">
+      <c r="H72" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31821,7 +32148,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F73" s="8" t="inlineStr">
         <is>
           <t>https://www.bigbinary.com/careers/react-native-engineer</t>
         </is>
@@ -31831,7 +32158,7 @@
           <t>Role not in target list: 'React Native Engineer&gt;RemoteCurrently not hiring'</t>
         </is>
       </c>
-      <c r="H73" s="5" t="n">
+      <c r="H73" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31856,7 +32183,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
+      <c r="F74" s="8" t="inlineStr">
         <is>
           <t>https://www.bigbinary.com/careers/react-js-engineer</t>
         </is>
@@ -31866,7 +32193,7 @@
           <t>Role not in target list: 'ReactJS Engineer&gt;RemoteCurrently not hiring'</t>
         </is>
       </c>
-      <c r="H74" s="5" t="n">
+      <c r="H74" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31891,7 +32218,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="F75" s="8" t="inlineStr">
         <is>
           <t>https://www.bigbinary.com/careers/ui-engineer</t>
         </is>
@@ -31901,7 +32228,7 @@
           <t>Role not in target list: 'Frontend UI Engineer&gt;RemoteCurrently not hiring'</t>
         </is>
       </c>
-      <c r="H75" s="5" t="n">
+      <c r="H75" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31926,7 +32253,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr">
+      <c r="F76" s="8" t="inlineStr">
         <is>
           <t>https://community.ebay.com/forum/ebay-developers-program-57950/</t>
         </is>
@@ -31936,7 +32263,7 @@
           <t>Role not in target list: 'eBay Developers Program'</t>
         </is>
       </c>
-      <c r="H76" s="5" t="n">
+      <c r="H76" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31961,7 +32288,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr">
+      <c r="F77" s="8" t="inlineStr">
         <is>
           <t>https://walkin.org/</t>
         </is>
@@ -31971,7 +32298,7 @@
           <t>Role not in target list: 'Walk In Counseling'</t>
         </is>
       </c>
-      <c r="H77" s="5" t="n">
+      <c r="H77" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -31997,7 +32324,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="F78" s="8" t="inlineStr">
         <is>
           <t>https://www.persistent.com/services/software-product-engineering/</t>
         </is>
@@ -32008,7 +32335,7 @@
                         Engineering'</t>
         </is>
       </c>
-      <c r="H78" s="5" t="n">
+      <c r="H78" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32034,7 +32361,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
+      <c r="F79" s="8" t="inlineStr">
         <is>
           <t>https://marketplace.persistentproducts.com/marketplace/#/storefront/taxonomy?categoryId=31&amp;level1Name=IOT&amp;level2Name=</t>
         </is>
@@ -32045,7 +32372,7 @@
     (IoT)'</t>
         </is>
       </c>
-      <c r="H79" s="5" t="n">
+      <c r="H79" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32070,7 +32397,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F80" s="3" t="inlineStr">
+      <c r="F80" s="8" t="inlineStr">
         <is>
           <t>https://www.kpit.com/expertise/virtual-engineering/</t>
         </is>
@@ -32080,7 +32407,7 @@
           <t>Role not in target list: 'Virtual Engineering'</t>
         </is>
       </c>
-      <c r="H80" s="5" t="n">
+      <c r="H80" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32105,7 +32432,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F81" s="3" t="inlineStr">
+      <c r="F81" s="8" t="inlineStr">
         <is>
           <t>https://www.kpit.com/expertise/vehicle-engineering-and-design/</t>
         </is>
@@ -32115,7 +32442,7 @@
           <t>Role not in target list: 'Vehicle Engineering &amp; Design'</t>
         </is>
       </c>
-      <c r="H81" s="5" t="n">
+      <c r="H81" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32140,7 +32467,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F82" s="3" t="inlineStr">
+      <c r="F82" s="8" t="inlineStr">
         <is>
           <t>https://www.forbes.com/lists/best-employers-for-engineers/</t>
         </is>
@@ -32150,7 +32477,7 @@
           <t>Role not in target list: 'Forbes Best Employers for EngineersEmerson is proud to be a '</t>
         </is>
       </c>
-      <c r="H82" s="5" t="n">
+      <c r="H82" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32175,7 +32502,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr">
+      <c r="F83" s="8" t="inlineStr">
         <is>
           <t>https://www.emerson.com/en/corporate/careers/military</t>
         </is>
@@ -32185,7 +32512,7 @@
           <t>Role not in target list: 'Veteran Careers and Transition Assistance ProgramsHiring ded'</t>
         </is>
       </c>
-      <c r="H83" s="5" t="n">
+      <c r="H83" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32210,7 +32537,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F84" s="3" t="inlineStr">
+      <c r="F84" s="8" t="inlineStr">
         <is>
           <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Bengaluru---Bellandur-GTP/Full-Stack-Engineer---Node---React-_JR1044648-1</t>
         </is>
@@ -32220,7 +32547,7 @@
           <t>Role not in target list: 'NodeFull Stack Engineer  (Node + React)Bengaluru'</t>
         </is>
       </c>
-      <c r="H84" s="5" t="n">
+      <c r="H84" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32245,7 +32572,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F85" s="3" t="inlineStr">
+      <c r="F85" s="8" t="inlineStr">
         <is>
           <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Bengaluru---Bellandur-GTP/Full-Stack-Engineer---Node---React-_JR1044647-1</t>
         </is>
@@ -32255,7 +32582,7 @@
           <t>Role not in target list: 'NodeFull Stack Engineer  (Node + React)Bengaluru'</t>
         </is>
       </c>
-      <c r="H85" s="5" t="n">
+      <c r="H85" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32280,7 +32607,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F86" s="3" t="inlineStr">
+      <c r="F86" s="8" t="inlineStr">
         <is>
           <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Bengaluru---Bellandur-GTP/Platform-Support-Engineer_JR1044543-1</t>
         </is>
@@ -32290,7 +32617,7 @@
           <t>Role not in target list: 'Other TechnologiesPlatform Support EngineerBengaluru'</t>
         </is>
       </c>
-      <c r="H86" s="5" t="n">
+      <c r="H86" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32315,7 +32642,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F87" s="3" t="inlineStr">
+      <c r="F87" s="8" t="inlineStr">
         <is>
           <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Bengaluru---Bellandur-GTP/Job-Title--Android-Engineer_JR1044604-1</t>
         </is>
@@ -32325,7 +32652,7 @@
           <t>Role not in target list: 'MobileJob Title: Android EngineerBengaluru'</t>
         </is>
       </c>
-      <c r="H87" s="5" t="n">
+      <c r="H87" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32350,7 +32677,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr">
+      <c r="F88" s="8" t="inlineStr">
         <is>
           <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Novi-Sad/AI-Architect_JR1044260-1</t>
         </is>
@@ -32360,7 +32687,7 @@
           <t>Role not in target list: 'AI/ML/Data ScienceSolution Architect (AI oriented)Novi Sad, '</t>
         </is>
       </c>
-      <c r="H88" s="5" t="n">
+      <c r="H88" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32385,7 +32712,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F89" s="3" t="inlineStr">
+      <c r="F89" s="8" t="inlineStr">
         <is>
           <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Belgrade/AI-Architect_JR1044256</t>
         </is>
@@ -32395,7 +32722,7 @@
           <t>Role not in target list: 'AI/ML/Data ScienceSolution Architect (AI oriented)Belgrade, '</t>
         </is>
       </c>
-      <c r="H89" s="5" t="n">
+      <c r="H89" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32420,7 +32747,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F90" s="3" t="inlineStr">
+      <c r="F90" s="8" t="inlineStr">
         <is>
           <t>https://www.bmc.com/it-solutions/bmc-ami-devx.html</t>
         </is>
@@ -32430,7 +32757,7 @@
           <t>Role not in target list: 'BMC AMI DevXEmpower next-gen developers with a mainframe-inc'</t>
         </is>
       </c>
-      <c r="H90" s="5" t="n">
+      <c r="H90" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32455,7 +32782,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F91" s="3" t="inlineStr">
+      <c r="F91" s="8" t="inlineStr">
         <is>
           <t>https://pubmatic.com/solutions/mobile/</t>
         </is>
@@ -32465,7 +32792,7 @@
           <t>Role not in target list: 'FOR APP DEVELOPERS'</t>
         </is>
       </c>
-      <c r="H91" s="5" t="n">
+      <c r="H91" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32490,7 +32817,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F92" s="3" t="inlineStr">
+      <c r="F92" s="8" t="inlineStr">
         <is>
           <t>https://pubmatic.com/careers/engineering/</t>
         </is>
@@ -32500,7 +32827,7 @@
           <t>Role not in target list: 'Engineering'</t>
         </is>
       </c>
-      <c r="H92" s="5" t="n">
+      <c r="H92" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32525,7 +32852,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F93" s="3" t="inlineStr">
+      <c r="F93" s="8" t="inlineStr">
         <is>
           <t>https://pubmatic.com/careers/engineering</t>
         </is>
@@ -32535,7 +32862,7 @@
           <t>Role not in target list: 'Engineering'</t>
         </is>
       </c>
-      <c r="H93" s="5" t="n">
+      <c r="H93" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32560,7 +32887,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F94" s="3" t="inlineStr">
+      <c r="F94" s="8" t="inlineStr">
         <is>
           <t>https://search.jobs.barclays/early-careers</t>
         </is>
@@ -32570,7 +32897,7 @@
           <t>Role not in target list: 'Graduates and internsOur graduate programmes and internships'</t>
         </is>
       </c>
-      <c r="H94" s="5" t="n">
+      <c r="H94" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32595,7 +32922,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F95" s="3" t="inlineStr">
+      <c r="F95" s="8" t="inlineStr">
         <is>
           <t>https://www.phonepe.com/careers/job-openings/?department=engineering</t>
         </is>
@@ -32605,7 +32932,7 @@
           <t>Role not in target list: 'Engineering'</t>
         </is>
       </c>
-      <c r="H95" s="5" t="n">
+      <c r="H95" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32630,7 +32957,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F96" s="3" t="inlineStr">
+      <c r="F96" s="8" t="inlineStr">
         <is>
           <t>https://www.wearemiq.com/careers?departments=sales-engineering</t>
         </is>
@@ -32640,7 +32967,7 @@
           <t>Role not in target list: 'Sales Engineering'</t>
         </is>
       </c>
-      <c r="H96" s="5" t="n">
+      <c r="H96" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32665,7 +32992,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F97" s="3" t="inlineStr">
+      <c r="F97" s="8" t="inlineStr">
         <is>
           <t>https://go.acceldata.io/isg-buyers-guide-data-quality-data-observability-2026</t>
         </is>
@@ -32675,7 +33002,7 @@
           <t>Role not in target list: 'Acceldata recognized as an Exemplary Leader in 2026 ISG Buye'</t>
         </is>
       </c>
-      <c r="H97" s="5" t="n">
+      <c r="H97" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32700,7 +33027,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F98" s="3" t="inlineStr">
+      <c r="F98" s="8" t="inlineStr">
         <is>
           <t>https://www.acceldata.io/platform</t>
         </is>
@@ -32710,7 +33037,7 @@
           <t>Role not in target list: 'xLake ArchitectureBuild and run intelligent data and AI pipe'</t>
         </is>
       </c>
-      <c r="H98" s="5" t="n">
+      <c r="H98" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32735,7 +33062,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F99" s="3" t="inlineStr">
+      <c r="F99" s="8" t="inlineStr">
         <is>
           <t>https://www.e-zest.com/digital-product-engineering-services</t>
         </is>
@@ -32745,7 +33072,7 @@
           <t>Role not in target list: 'Product Engineering'</t>
         </is>
       </c>
-      <c r="H99" s="5" t="n">
+      <c r="H99" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32770,7 +33097,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F100" s="3" t="inlineStr">
+      <c r="F100" s="8" t="inlineStr">
         <is>
           <t>https://www.e-zest.com/engineering-lead</t>
         </is>
@@ -32780,7 +33107,7 @@
           <t>Role not in target list: 'Engineering Lead'</t>
         </is>
       </c>
-      <c r="H100" s="5" t="n">
+      <c r="H100" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32805,7 +33132,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F101" s="3" t="inlineStr">
+      <c r="F101" s="8" t="inlineStr">
         <is>
           <t>https://www.e-zest.com/sr-kafka-engineer</t>
         </is>
@@ -32815,7 +33142,7 @@
           <t>Role not in target list: 'Sr. Kafka Engineer'</t>
         </is>
       </c>
-      <c r="H101" s="5" t="n">
+      <c r="H101" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32840,7 +33167,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F102" s="3" t="inlineStr">
+      <c r="F102" s="8" t="inlineStr">
         <is>
           <t>https://www.e-zest.com/sr-node-developer</t>
         </is>
@@ -32850,7 +33177,7 @@
           <t>Role not in target list: 'Sr. Node Developer'</t>
         </is>
       </c>
-      <c r="H102" s="5" t="n">
+      <c r="H102" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32875,7 +33202,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F103" s="3" t="inlineStr">
+      <c r="F103" s="8" t="inlineStr">
         <is>
           <t>https://www.e-zest.com/sr-react-developer</t>
         </is>
@@ -32885,7 +33212,7 @@
           <t>Role not in target list: 'Sr. React Developer'</t>
         </is>
       </c>
-      <c r="H103" s="5" t="n">
+      <c r="H103" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32910,7 +33237,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F104" s="3" t="inlineStr">
+      <c r="F104" s="8" t="inlineStr">
         <is>
           <t>https://www.e-zest.com/sr-automation-test-engineer</t>
         </is>
@@ -32920,7 +33247,7 @@
           <t>Role not in target list: 'Sr. Automation Test Engineer'</t>
         </is>
       </c>
-      <c r="H104" s="5" t="n">
+      <c r="H104" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32945,7 +33272,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F105" s="3" t="inlineStr">
+      <c r="F105" s="8" t="inlineStr">
         <is>
           <t>https://dbs.wd3.myworkdayjobs.com/DBS_Careers</t>
         </is>
@@ -32955,7 +33282,7 @@
           <t>Role not in target list: 'International Centres'</t>
         </is>
       </c>
-      <c r="H105" s="5" t="n">
+      <c r="H105" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -32980,7 +33307,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F106" s="3" t="inlineStr">
+      <c r="F106" s="8" t="inlineStr">
         <is>
           <t>https://www.dbs.com/careers/internships/default.page</t>
         </is>
@@ -32990,7 +33317,7 @@
           <t>Role not in target list: 'Internships'</t>
         </is>
       </c>
-      <c r="H106" s="5" t="n">
+      <c r="H106" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33015,7 +33342,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F107" s="3" t="inlineStr">
+      <c r="F107" s="8" t="inlineStr">
         <is>
           <t>https://khoros.ai/developer/</t>
         </is>
@@ -33025,7 +33352,7 @@
           <t>Role not in target list: 'Developer Portal'</t>
         </is>
       </c>
-      <c r="H107" s="5" t="n">
+      <c r="H107" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33050,7 +33377,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F108" s="3" t="inlineStr">
+      <c r="F108" s="8" t="inlineStr">
         <is>
           <t>https://razorpay.com/accept-international-payments/</t>
         </is>
@@ -33060,7 +33387,7 @@
           <t>Role not in target list: 'International Payments'</t>
         </is>
       </c>
-      <c r="H108" s="5" t="n">
+      <c r="H108" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33085,7 +33412,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F109" s="3" t="inlineStr">
+      <c r="F109" s="8" t="inlineStr">
         <is>
           <t>https://razorpay.com/docs/</t>
         </is>
@@ -33095,7 +33422,7 @@
           <t>Role not in target list: 'Developer Docs'</t>
         </is>
       </c>
-      <c r="H109" s="5" t="n">
+      <c r="H109" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33120,7 +33447,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F110" s="3" t="inlineStr">
+      <c r="F110" s="8" t="inlineStr">
         <is>
           <t>https://razorpay.com/careers/#ai-builders</t>
         </is>
@@ -33130,7 +33457,7 @@
           <t>Role not in target list: 'HiringAI Builders'</t>
         </is>
       </c>
-      <c r="H110" s="5" t="n">
+      <c r="H110" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33155,7 +33482,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F111" s="3" t="inlineStr">
+      <c r="F111" s="8" t="inlineStr">
         <is>
           <t>https://razorpay.com/ai-builders/</t>
         </is>
@@ -33165,7 +33492,7 @@
           <t>Role not in target list: 'Hiring the MostObsessed AI BuildersHiring the MostObsessed A'</t>
         </is>
       </c>
-      <c r="H111" s="5" t="n">
+      <c r="H111" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33190,7 +33517,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F112" s="3" t="inlineStr">
+      <c r="F112" s="8" t="inlineStr">
         <is>
           <t>https://www.atlassian.com/company/careers/all-jobs?team=Engineering%2CIT%2CSecurity%2CSite%20Reliability%20Engineering&amp;location=&amp;search=</t>
         </is>
@@ -33200,7 +33527,7 @@
           <t>Role not in target list: 'Engineering'</t>
         </is>
       </c>
-      <c r="H112" s="5" t="n">
+      <c r="H112" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33225,7 +33552,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F113" s="3" t="inlineStr">
+      <c r="F113" s="8" t="inlineStr">
         <is>
           <t>https://www.atlassian.com/company/careers/all-jobs?team=Engineering&amp;location=&amp;search=</t>
         </is>
@@ -33235,7 +33562,7 @@
           <t>Role not in target list: 'Browse all engineering roles'</t>
         </is>
       </c>
-      <c r="H113" s="5" t="n">
+      <c r="H113" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33260,7 +33587,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F114" s="3" t="inlineStr">
+      <c r="F114" s="8" t="inlineStr">
         <is>
           <t>https://www.atlassian.com/company/careers/earlycareers</t>
         </is>
@@ -33270,7 +33597,7 @@
           <t>Role not in target list: 'student and internship opportunities'</t>
         </is>
       </c>
-      <c r="H114" s="5" t="n">
+      <c r="H114" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33295,7 +33622,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F115" s="3" t="inlineStr">
+      <c r="F115" s="8" t="inlineStr">
         <is>
           <t>https://docs.clevertap.com/docs/getting-started</t>
         </is>
@@ -33305,7 +33632,7 @@
           <t>Role not in target list: 'User DocumentationUser and Developer Docs for learning Cleve'</t>
         </is>
       </c>
-      <c r="H115" s="5" t="n">
+      <c r="H115" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33330,7 +33657,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F116" s="3" t="inlineStr">
+      <c r="F116" s="8" t="inlineStr">
         <is>
           <t>https://www.moengage.com/role/for-developers/</t>
         </is>
@@ -33340,7 +33667,7 @@
           <t>Role not in target list: 'For Developers'</t>
         </is>
       </c>
-      <c r="H116" s="5" t="n">
+      <c r="H116" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33365,7 +33692,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F117" s="3" t="inlineStr">
+      <c r="F117" s="8" t="inlineStr">
         <is>
           <t>https://www.moengage.com/docs/developer-guide/introduction</t>
         </is>
@@ -33375,7 +33702,7 @@
           <t>Role not in target list: 'Developer Hub'</t>
         </is>
       </c>
-      <c r="H117" s="5" t="n">
+      <c r="H117" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33400,7 +33727,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F118" s="3" t="inlineStr">
+      <c r="F118" s="8" t="inlineStr">
         <is>
           <t>https://www.emerson.com/en/corporate/about-us/living-our-purpose</t>
         </is>
@@ -33410,7 +33737,7 @@
           <t>Role not in target list: 'Living Our PurposeWe drive innovation that makes the world h'</t>
         </is>
       </c>
-      <c r="H118" s="5" t="n">
+      <c r="H118" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33435,7 +33762,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F119" s="3" t="inlineStr">
+      <c r="F119" s="8" t="inlineStr">
         <is>
           <t>https://www.acceldata.io/capabilities/ai-pipelines</t>
         </is>
@@ -33445,7 +33772,7 @@
           <t>Role not in target list: 'AI PipelinesDesign and run autonomous HITL workflows orchest'</t>
         </is>
       </c>
-      <c r="H119" s="5" t="n">
+      <c r="H119" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33470,7 +33797,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F120" s="3" t="inlineStr">
+      <c r="F120" s="8" t="inlineStr">
         <is>
           <t>https://www.zenoti.com/platform/ai-lead-management</t>
         </is>
@@ -33480,7 +33807,7 @@
           <t>Role not in target list: 'AI Lead Management'</t>
         </is>
       </c>
-      <c r="H120" s="5" t="n">
+      <c r="H120" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33505,7 +33832,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F121" s="3" t="inlineStr">
+      <c r="F121" s="8" t="inlineStr">
         <is>
           <t>https://leena.ai/agentic-ai-architecture</t>
         </is>
@@ -33515,7 +33842,7 @@
           <t>Role not in target list: 'Agentic AI Architecture Overview'</t>
         </is>
       </c>
-      <c r="H121" s="5" t="n">
+      <c r="H121" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33540,7 +33867,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F122" s="3" t="inlineStr">
+      <c r="F122" s="8" t="inlineStr">
         <is>
           <t>https://atlan.com/careers/#job-list</t>
         </is>
@@ -33550,7 +33877,7 @@
           <t>Role not in target list: 'See roles that match these traits'</t>
         </is>
       </c>
-      <c r="H122" s="5" t="n">
+      <c r="H122" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33575,7 +33902,7 @@
           <t>0-1 years</t>
         </is>
       </c>
-      <c r="F123" s="3" t="inlineStr">
+      <c r="F123" s="8" t="inlineStr">
         <is>
           <t>https://clevertap.com/events/cleverai-summit-2026/?utm_source=top-hat-banner&amp;utm_medium=organic&amp;utm_campaign=aisummit-2026-event</t>
         </is>
@@ -33585,7 +33912,2321 @@
           <t>Role not in target list: 'See 1:1 AI-Driven Personalization in ActionRequest your Invi'</t>
         </is>
       </c>
-      <c r="H123" s="5" t="n">
+      <c r="H123" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>Moneycontrol</t>
+        </is>
+      </c>
+      <c r="B124" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pune engineering freshers face toughest job market in years </t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="D124" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F124" s="8" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/city/pune-s-fresh-engineering-graduates-face-toughest-job-market-in-years-as-it-companies-slow-entry-level-hiring-article-13939232.html</t>
+        </is>
+      </c>
+      <c r="G124" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Pune engineering freshers face toughest job market in years '</t>
+        </is>
+      </c>
+      <c r="H124" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>News18</t>
+        </is>
+      </c>
+      <c r="B125" s="1" t="inlineStr">
+        <is>
+          <t>Infosys Starting Salary For Freshers In 2026: AI Roles, Rs 2</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D125" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F125" s="8" t="inlineStr">
+        <is>
+          <t>https://www.news18.com/photogallery/business/economy/infosys-starting-salary-for-freshers-in-2026-ai-roles-rs-21-lakh-packages-and-more-ws-l-10224973.html</t>
+        </is>
+      </c>
+      <c r="G125" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Infosys Starting Salary For Freshers In 2026: AI Roles, Rs 2'</t>
+        </is>
+      </c>
+      <c r="H125" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>Indianexpress</t>
+        </is>
+      </c>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t>Fresher hiring rises to 75%, but where are young Indians fin</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F126" s="8" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/education/international-youth-day-fresher-hiring-trends-rises-75-percent-where-young-indians-actually-finding-jobs-top-domains-salary-10829381/</t>
+        </is>
+      </c>
+      <c r="G126" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Fresher hiring rises to 75%, but where are young Indians fin'</t>
+        </is>
+      </c>
+      <c r="H126" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>Ndtv</t>
+        </is>
+      </c>
+      <c r="B127" s="1" t="inlineStr">
+        <is>
+          <t>Viral Video Shows 3,000 Engineers Queuing Up For Walk-In Job</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="D127" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F127" s="8" t="inlineStr">
+        <is>
+          <t>https://www.ndtv.com/india-news/viral-video-shows-3-000-engineers-queuing-up-for-walk-in-job-interview-in-pune-4938186</t>
+        </is>
+      </c>
+      <c r="G127" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Viral Video Shows 3,000 Engineers Queuing Up For Walk-In Job'</t>
+        </is>
+      </c>
+      <c r="H127" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>Msn</t>
+        </is>
+      </c>
+      <c r="B128" s="1" t="inlineStr">
+        <is>
+          <t>Retail, e-commerce to drive fresher hiring in Pune</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="D128" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F128" s="8" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/other/retail-e-commerce-to-drive-fresher-hiring-in-pune/ar-AA29Ii38</t>
+        </is>
+      </c>
+      <c r="G128" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Retail, e-commerce to drive fresher hiring in Pune'</t>
+        </is>
+      </c>
+      <c r="H128" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>Timesofindia</t>
+        </is>
+      </c>
+      <c r="B129" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fresher hiring rises to 73% in early 2026, but the rules of </t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D129" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F129" s="8" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/education/careers/news/fresher-hiring-rises-to-73-in-early-2026-but-the-rules-of-entry-have-changed/articleshow/128504926.cms</t>
+        </is>
+      </c>
+      <c r="G129" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Fresher hiring rises to 73% in early 2026, but the rules of '</t>
+        </is>
+      </c>
+      <c r="H129" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>Analyticsinsight</t>
+        </is>
+      </c>
+      <c r="B130" s="1" t="inlineStr">
+        <is>
+          <t>Top Tech Companies Hiring Freshers in India, the US in 2026</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D130" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F130" s="8" t="inlineStr">
+        <is>
+          <t>https://www.analyticsinsight.net/companies/top-tech-companies-hiring-freshers-in-india-the-us-in-2026</t>
+        </is>
+      </c>
+      <c r="G130" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Top Tech Companies Hiring Freshers in India, the US in 2026'</t>
+        </is>
+      </c>
+      <c r="H130" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>Msn</t>
+        </is>
+      </c>
+      <c r="B131" s="1" t="inlineStr">
+        <is>
+          <t>AI, GCCs and a changing job market: India's fresher hiring i</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F131" s="8" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/careers/job-search/ai-gccs-and-a-changing-job-market-india-s-fresher-hiring-is-no-longer-just-an-it-story-who-s-driving-the-shift/ar-AA29wtdN</t>
+        </is>
+      </c>
+      <c r="G131" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'AI, GCCs and a changing job market: India's fresher hiring i'</t>
+        </is>
+      </c>
+      <c r="H131" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t>Fresher hiring gains in manufacturing, retail as IT demand c</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D132" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F132" s="8" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/industry/news/fresher-hiring-gains-in-manufacturing-retail-as-it-demand-cools-report-126081001534_1.html</t>
+        </is>
+      </c>
+      <c r="G132" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Fresher hiring gains in manufacturing, retail as IT demand c'</t>
+        </is>
+      </c>
+      <c r="H132" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>Careerindia</t>
+        </is>
+      </c>
+      <c r="B133" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">August Hiring Surge: Top AI and Non-IT Jobs for Freshers to </t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D133" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F133" s="8" t="inlineStr">
+        <is>
+          <t>https://www.careerindia.com/tips/india-hiring-surge-2026-best-ai-non-it-jobs-career-guide-011-65453.html</t>
+        </is>
+      </c>
+      <c r="G133" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'August Hiring Surge: Top AI and Non-IT Jobs for Freshers to '</t>
+        </is>
+      </c>
+      <c r="H133" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>Systemdesignhandbook</t>
+        </is>
+      </c>
+      <c r="B134" s="1" t="inlineStr">
+        <is>
+          <t>Backend Engineering: Complete Guide for Modern Backend Engin</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D134" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F134" s="8" t="inlineStr">
+        <is>
+          <t>https://www.systemdesignhandbook.com/guides/backend-engineers/</t>
+        </is>
+      </c>
+      <c r="G134" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Backend Engineering: Complete Guide for Modern Backend Engin'</t>
+        </is>
+      </c>
+      <c r="H134" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="B135" s="1" t="inlineStr">
+        <is>
+          <t>Fresher Java Developer jobs in Hyderabad</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="D135" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F135" s="8" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/job-search/fresher-java-developer-jobs-in-hyderabad</t>
+        </is>
+      </c>
+      <c r="G135" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Fresher Java Developer jobs in Hyderabad'</t>
+        </is>
+      </c>
+      <c r="H135" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>Tcsion</t>
+        </is>
+      </c>
+      <c r="B136" s="1" t="inlineStr">
+        <is>
+          <t>Fresher Jobs in Hyderabad</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="D136" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F136" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tcsion.com/job-openings/fresher-jobs-in-hyderabad</t>
+        </is>
+      </c>
+      <c r="G136" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Fresher Jobs in Hyderabad'</t>
+        </is>
+      </c>
+      <c r="H136" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>Mayoclinic</t>
+        </is>
+      </c>
+      <c r="B137" s="1" t="inlineStr">
+        <is>
+          <t>Walking: Trim your waistline, improve your health</t>
+        </is>
+      </c>
+      <c r="C137" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D137" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F137" s="8" t="inlineStr">
+        <is>
+          <t>https://www.mayoclinic.org/healthy-lifestyle/fitness/in-depth/walking/art-20046261</t>
+        </is>
+      </c>
+      <c r="G137" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Walking: Trim your waistline, improve your health'</t>
+        </is>
+      </c>
+      <c r="H137" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>Timesofindia</t>
+        </is>
+      </c>
+      <c r="B138" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freshers throng tech parks for walk-in jobs as hiring slows </t>
+        </is>
+      </c>
+      <c r="C138" s="1" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="D138" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F138" s="8" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/freshers-throng-tech-parks-for-walk-in-jobs-as-hiring-slows-down/articleshow/118155099.cms</t>
+        </is>
+      </c>
+      <c r="G138" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Freshers throng tech parks for walk-in jobs as hiring slows '</t>
+        </is>
+      </c>
+      <c r="H138" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>BigBinary</t>
+        </is>
+      </c>
+      <c r="B139" s="1" t="inlineStr">
+        <is>
+          <t>Ruby on Rails Engineer&gt;RemoteCurrently not hiring</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D139" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F139" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bigbinary.com/careers/ruby-on-rails-engineer</t>
+        </is>
+      </c>
+      <c r="G139" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Ruby on Rails Engineer&gt;RemoteCurrently not hiring'</t>
+        </is>
+      </c>
+      <c r="H139" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>BigBinary</t>
+        </is>
+      </c>
+      <c r="B140" s="1" t="inlineStr">
+        <is>
+          <t>React Native Engineer&gt;RemoteCurrently not hiring</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D140" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F140" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bigbinary.com/careers/react-native-engineer</t>
+        </is>
+      </c>
+      <c r="G140" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'React Native Engineer&gt;RemoteCurrently not hiring'</t>
+        </is>
+      </c>
+      <c r="H140" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>BigBinary</t>
+        </is>
+      </c>
+      <c r="B141" s="1" t="inlineStr">
+        <is>
+          <t>ReactJS Engineer&gt;RemoteCurrently not hiring</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D141" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F141" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bigbinary.com/careers/react-js-engineer</t>
+        </is>
+      </c>
+      <c r="G141" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'ReactJS Engineer&gt;RemoteCurrently not hiring'</t>
+        </is>
+      </c>
+      <c r="H141" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>BigBinary</t>
+        </is>
+      </c>
+      <c r="B142" s="1" t="inlineStr">
+        <is>
+          <t>Frontend UI Engineer&gt;RemoteCurrently not hiring</t>
+        </is>
+      </c>
+      <c r="C142" s="1" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D142" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F142" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bigbinary.com/careers/ui-engineer</t>
+        </is>
+      </c>
+      <c r="G142" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Frontend UI Engineer&gt;RemoteCurrently not hiring'</t>
+        </is>
+      </c>
+      <c r="H142" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>Freepressjournal</t>
+        </is>
+      </c>
+      <c r="B143" s="1" t="inlineStr">
+        <is>
+          <t>Pune: Engineering Admissions Rise By 15,181 Across Maharasht</t>
+        </is>
+      </c>
+      <c r="C143" s="1" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="D143" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F143" s="8" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/pune/pune-engineering-admissions-rise-by-15181-across-maharashtra-151-lakh-students-secure-seats</t>
+        </is>
+      </c>
+      <c r="G143" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Pune: Engineering Admissions Rise By 15,181 Across Maharasht'</t>
+        </is>
+      </c>
+      <c r="H143" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>Persistent Systems</t>
+        </is>
+      </c>
+      <c r="B144" s="1" t="inlineStr">
+        <is>
+          <t>Software Product
+                        Engineering</t>
+        </is>
+      </c>
+      <c r="C144" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D144" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F144" s="8" t="inlineStr">
+        <is>
+          <t>https://www.persistent.com/services/software-product-engineering/</t>
+        </is>
+      </c>
+      <c r="G144" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Software Product
+                        Engineering'</t>
+        </is>
+      </c>
+      <c r="H144" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>Persistent Systems</t>
+        </is>
+      </c>
+      <c r="B145" s="1" t="inlineStr">
+        <is>
+          <t>Internet of Things
+    (IoT)</t>
+        </is>
+      </c>
+      <c r="C145" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D145" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F145" s="8" t="inlineStr">
+        <is>
+          <t>https://marketplace.persistentproducts.com/marketplace/#/storefront/taxonomy?categoryId=31&amp;level1Name=IOT&amp;level2Name=</t>
+        </is>
+      </c>
+      <c r="G145" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Internet of Things
+    (IoT)'</t>
+        </is>
+      </c>
+      <c r="H145" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>KPIT Technologies</t>
+        </is>
+      </c>
+      <c r="B146" s="1" t="inlineStr">
+        <is>
+          <t>Virtual Engineering</t>
+        </is>
+      </c>
+      <c r="C146" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D146" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F146" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kpit.com/expertise/virtual-engineering/</t>
+        </is>
+      </c>
+      <c r="G146" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Virtual Engineering'</t>
+        </is>
+      </c>
+      <c r="H146" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>KPIT Technologies</t>
+        </is>
+      </c>
+      <c r="B147" s="1" t="inlineStr">
+        <is>
+          <t>Vehicle Engineering &amp; Design</t>
+        </is>
+      </c>
+      <c r="C147" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D147" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F147" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kpit.com/expertise/vehicle-engineering-and-design/</t>
+        </is>
+      </c>
+      <c r="G147" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Vehicle Engineering &amp; Design'</t>
+        </is>
+      </c>
+      <c r="H147" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="B148" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forbes Best Employers for EngineersEmerson is proud to be a </t>
+        </is>
+      </c>
+      <c r="C148" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D148" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F148" s="8" t="inlineStr">
+        <is>
+          <t>https://www.forbes.com/lists/best-employers-for-engineers/</t>
+        </is>
+      </c>
+      <c r="G148" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Forbes Best Employers for EngineersEmerson is proud to be a '</t>
+        </is>
+      </c>
+      <c r="H148" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="B149" s="1" t="inlineStr">
+        <is>
+          <t>Veteran Careers and Transition Assistance ProgramsHiring ded</t>
+        </is>
+      </c>
+      <c r="C149" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D149" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F149" s="8" t="inlineStr">
+        <is>
+          <t>https://www.emerson.com/en/corporate/careers/military</t>
+        </is>
+      </c>
+      <c r="G149" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Veteran Careers and Transition Assistance ProgramsHiring ded'</t>
+        </is>
+      </c>
+      <c r="H149" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>Synechron</t>
+        </is>
+      </c>
+      <c r="B150" s="1" t="inlineStr">
+        <is>
+          <t>Other TechnologiesRPGLE DeveloperBengaluru</t>
+        </is>
+      </c>
+      <c r="C150" s="1" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="D150" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F150" s="8" t="inlineStr">
+        <is>
+          <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Bengaluru---EC-2-Gateway-campus/RPGLE-Developer_JR1044673-1</t>
+        </is>
+      </c>
+      <c r="G150" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Other TechnologiesRPGLE DeveloperBengaluru'</t>
+        </is>
+      </c>
+      <c r="H150" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>Synechron</t>
+        </is>
+      </c>
+      <c r="B151" s="1" t="inlineStr">
+        <is>
+          <t>Other TechnologiesConnex DeveloperChennai</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D151" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F151" s="8" t="inlineStr">
+        <is>
+          <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Chennai---Taramani-Ascendas/Connex-Developer_JR1044658</t>
+        </is>
+      </c>
+      <c r="G151" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Other TechnologiesConnex DeveloperChennai'</t>
+        </is>
+      </c>
+      <c r="H151" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>Synechron</t>
+        </is>
+      </c>
+      <c r="B152" s="1" t="inlineStr">
+        <is>
+          <t>NodeFull Stack Engineer  (Node + React)Bengaluru</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="D152" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F152" s="8" t="inlineStr">
+        <is>
+          <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Bengaluru---Bellandur-GTP/Full-Stack-Engineer---Node---React-_JR1044648-1</t>
+        </is>
+      </c>
+      <c r="G152" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'NodeFull Stack Engineer  (Node + React)Bengaluru'</t>
+        </is>
+      </c>
+      <c r="H152" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>Synechron</t>
+        </is>
+      </c>
+      <c r="B153" s="1" t="inlineStr">
+        <is>
+          <t>NodeFull Stack Engineer  (Node + React)Bengaluru</t>
+        </is>
+      </c>
+      <c r="C153" s="1" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="D153" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F153" s="8" t="inlineStr">
+        <is>
+          <t>https://synechron.wd1.myworkdayjobs.com/SynechronCareers/job/Bengaluru---Bellandur-GTP/Full-Stack-Engineer---Node---React-_JR1044647-1</t>
+        </is>
+      </c>
+      <c r="G153" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'NodeFull Stack Engineer  (Node + React)Bengaluru'</t>
+        </is>
+      </c>
+      <c r="H153" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>BMC Software</t>
+        </is>
+      </c>
+      <c r="B154" s="1" t="inlineStr">
+        <is>
+          <t>BMC AMI DevXEmpower next-gen developers with a mainframe-inc</t>
+        </is>
+      </c>
+      <c r="C154" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D154" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F154" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bmc.com/it-solutions/bmc-ami-devx.html</t>
+        </is>
+      </c>
+      <c r="G154" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'BMC AMI DevXEmpower next-gen developers with a mainframe-inc'</t>
+        </is>
+      </c>
+      <c r="H154" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>Pubmatic</t>
+        </is>
+      </c>
+      <c r="B155" s="1" t="inlineStr">
+        <is>
+          <t>FOR APP DEVELOPERS</t>
+        </is>
+      </c>
+      <c r="C155" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D155" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F155" s="8" t="inlineStr">
+        <is>
+          <t>https://pubmatic.com/solutions/mobile/</t>
+        </is>
+      </c>
+      <c r="G155" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'FOR APP DEVELOPERS'</t>
+        </is>
+      </c>
+      <c r="H155" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>Pubmatic</t>
+        </is>
+      </c>
+      <c r="B156" s="1" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="C156" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D156" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F156" s="8" t="inlineStr">
+        <is>
+          <t>https://pubmatic.com/careers/engineering/</t>
+        </is>
+      </c>
+      <c r="G156" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Engineering'</t>
+        </is>
+      </c>
+      <c r="H156" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>Pubmatic</t>
+        </is>
+      </c>
+      <c r="B157" s="1" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="C157" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D157" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F157" s="8" t="inlineStr">
+        <is>
+          <t>https://pubmatic.com/careers/engineering</t>
+        </is>
+      </c>
+      <c r="G157" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Engineering'</t>
+        </is>
+      </c>
+      <c r="H157" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>Barclays</t>
+        </is>
+      </c>
+      <c r="B158" s="1" t="inlineStr">
+        <is>
+          <t>Graduates and internsOur graduate programmes and internships</t>
+        </is>
+      </c>
+      <c r="C158" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D158" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F158" s="8" t="inlineStr">
+        <is>
+          <t>https://search.jobs.barclays/early-careers</t>
+        </is>
+      </c>
+      <c r="G158" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Graduates and internsOur graduate programmes and internships'</t>
+        </is>
+      </c>
+      <c r="H158" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>PhonePe</t>
+        </is>
+      </c>
+      <c r="B159" s="1" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="C159" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D159" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F159" s="8" t="inlineStr">
+        <is>
+          <t>https://www.phonepe.com/careers/job-openings/?department=engineering</t>
+        </is>
+      </c>
+      <c r="G159" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Engineering'</t>
+        </is>
+      </c>
+      <c r="H159" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>MiQ</t>
+        </is>
+      </c>
+      <c r="B160" s="1" t="inlineStr">
+        <is>
+          <t>Sales Engineering</t>
+        </is>
+      </c>
+      <c r="C160" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D160" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F160" s="8" t="inlineStr">
+        <is>
+          <t>https://www.wearemiq.com/careers?departments=sales-engineering</t>
+        </is>
+      </c>
+      <c r="G160" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Sales Engineering'</t>
+        </is>
+      </c>
+      <c r="H160" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>Acceldata</t>
+        </is>
+      </c>
+      <c r="B161" s="1" t="inlineStr">
+        <is>
+          <t>Acceldata recognized as an Exemplary Leader in 2026 ISG Buye</t>
+        </is>
+      </c>
+      <c r="C161" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D161" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F161" s="8" t="inlineStr">
+        <is>
+          <t>https://go.acceldata.io/isg-buyers-guide-data-quality-data-observability-2026</t>
+        </is>
+      </c>
+      <c r="G161" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Acceldata recognized as an Exemplary Leader in 2026 ISG Buye'</t>
+        </is>
+      </c>
+      <c r="H161" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>Acceldata</t>
+        </is>
+      </c>
+      <c r="B162" s="1" t="inlineStr">
+        <is>
+          <t>xLake ArchitectureBuild and run intelligent data and AI pipe</t>
+        </is>
+      </c>
+      <c r="C162" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D162" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F162" s="8" t="inlineStr">
+        <is>
+          <t>https://www.acceldata.io/platform</t>
+        </is>
+      </c>
+      <c r="G162" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'xLake ArchitectureBuild and run intelligent data and AI pipe'</t>
+        </is>
+      </c>
+      <c r="H162" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>e-Zest Solutions</t>
+        </is>
+      </c>
+      <c r="B163" s="1" t="inlineStr">
+        <is>
+          <t>Product Engineering</t>
+        </is>
+      </c>
+      <c r="C163" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D163" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F163" s="8" t="inlineStr">
+        <is>
+          <t>https://www.e-zest.com/digital-product-engineering-services</t>
+        </is>
+      </c>
+      <c r="G163" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Product Engineering'</t>
+        </is>
+      </c>
+      <c r="H163" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>e-Zest Solutions</t>
+        </is>
+      </c>
+      <c r="B164" s="1" t="inlineStr">
+        <is>
+          <t>Engineering Lead</t>
+        </is>
+      </c>
+      <c r="C164" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D164" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F164" s="8" t="inlineStr">
+        <is>
+          <t>https://www.e-zest.com/engineering-lead</t>
+        </is>
+      </c>
+      <c r="G164" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Engineering Lead'</t>
+        </is>
+      </c>
+      <c r="H164" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>e-Zest Solutions</t>
+        </is>
+      </c>
+      <c r="B165" s="1" t="inlineStr">
+        <is>
+          <t>Sr. Kafka Engineer</t>
+        </is>
+      </c>
+      <c r="C165" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D165" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F165" s="8" t="inlineStr">
+        <is>
+          <t>https://www.e-zest.com/sr-kafka-engineer</t>
+        </is>
+      </c>
+      <c r="G165" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Sr. Kafka Engineer'</t>
+        </is>
+      </c>
+      <c r="H165" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>e-Zest Solutions</t>
+        </is>
+      </c>
+      <c r="B166" s="1" t="inlineStr">
+        <is>
+          <t>Sr. Node Developer</t>
+        </is>
+      </c>
+      <c r="C166" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D166" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F166" s="8" t="inlineStr">
+        <is>
+          <t>https://www.e-zest.com/sr-node-developer</t>
+        </is>
+      </c>
+      <c r="G166" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Sr. Node Developer'</t>
+        </is>
+      </c>
+      <c r="H166" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>e-Zest Solutions</t>
+        </is>
+      </c>
+      <c r="B167" s="1" t="inlineStr">
+        <is>
+          <t>Sr. React Developer</t>
+        </is>
+      </c>
+      <c r="C167" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D167" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F167" s="8" t="inlineStr">
+        <is>
+          <t>https://www.e-zest.com/sr-react-developer</t>
+        </is>
+      </c>
+      <c r="G167" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Sr. React Developer'</t>
+        </is>
+      </c>
+      <c r="H167" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>e-Zest Solutions</t>
+        </is>
+      </c>
+      <c r="B168" s="1" t="inlineStr">
+        <is>
+          <t>Sr. Automation Test Engineer</t>
+        </is>
+      </c>
+      <c r="C168" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D168" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F168" s="8" t="inlineStr">
+        <is>
+          <t>https://www.e-zest.com/sr-automation-test-engineer</t>
+        </is>
+      </c>
+      <c r="G168" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Sr. Automation Test Engineer'</t>
+        </is>
+      </c>
+      <c r="H168" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>DBS Bank</t>
+        </is>
+      </c>
+      <c r="B169" s="1" t="inlineStr">
+        <is>
+          <t>International Centres</t>
+        </is>
+      </c>
+      <c r="C169" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D169" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F169" s="8" t="inlineStr">
+        <is>
+          <t>https://dbs.wd3.myworkdayjobs.com/DBS_Careers</t>
+        </is>
+      </c>
+      <c r="G169" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'International Centres'</t>
+        </is>
+      </c>
+      <c r="H169" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>DBS Bank</t>
+        </is>
+      </c>
+      <c r="B170" s="1" t="inlineStr">
+        <is>
+          <t>Internships</t>
+        </is>
+      </c>
+      <c r="C170" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D170" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F170" s="8" t="inlineStr">
+        <is>
+          <t>https://www.dbs.com/careers/internships/default.page</t>
+        </is>
+      </c>
+      <c r="G170" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Internships'</t>
+        </is>
+      </c>
+      <c r="H170" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>Khoros</t>
+        </is>
+      </c>
+      <c r="B171" s="1" t="inlineStr">
+        <is>
+          <t>Developer Portal</t>
+        </is>
+      </c>
+      <c r="C171" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D171" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F171" s="8" t="inlineStr">
+        <is>
+          <t>https://khoros.ai/developer/</t>
+        </is>
+      </c>
+      <c r="G171" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Developer Portal'</t>
+        </is>
+      </c>
+      <c r="H171" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>Razorpay</t>
+        </is>
+      </c>
+      <c r="B172" s="1" t="inlineStr">
+        <is>
+          <t>International Payments</t>
+        </is>
+      </c>
+      <c r="C172" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D172" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F172" s="8" t="inlineStr">
+        <is>
+          <t>https://razorpay.com/accept-international-payments/</t>
+        </is>
+      </c>
+      <c r="G172" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'International Payments'</t>
+        </is>
+      </c>
+      <c r="H172" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>Razorpay</t>
+        </is>
+      </c>
+      <c r="B173" s="1" t="inlineStr">
+        <is>
+          <t>Developer Docs</t>
+        </is>
+      </c>
+      <c r="C173" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D173" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F173" s="8" t="inlineStr">
+        <is>
+          <t>https://razorpay.com/docs/</t>
+        </is>
+      </c>
+      <c r="G173" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Developer Docs'</t>
+        </is>
+      </c>
+      <c r="H173" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>Razorpay</t>
+        </is>
+      </c>
+      <c r="B174" s="1" t="inlineStr">
+        <is>
+          <t>HiringAI Builders</t>
+        </is>
+      </c>
+      <c r="C174" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D174" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F174" s="8" t="inlineStr">
+        <is>
+          <t>https://razorpay.com/careers/#ai-builders</t>
+        </is>
+      </c>
+      <c r="G174" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'HiringAI Builders'</t>
+        </is>
+      </c>
+      <c r="H174" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>Razorpay</t>
+        </is>
+      </c>
+      <c r="B175" s="1" t="inlineStr">
+        <is>
+          <t>Hiring the MostObsessed AI BuildersHiring the MostObsessed A</t>
+        </is>
+      </c>
+      <c r="C175" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D175" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F175" s="8" t="inlineStr">
+        <is>
+          <t>https://razorpay.com/ai-builders/</t>
+        </is>
+      </c>
+      <c r="G175" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Hiring the MostObsessed AI BuildersHiring the MostObsessed A'</t>
+        </is>
+      </c>
+      <c r="H175" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="B176" s="1" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="C176" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D176" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F176" s="8" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/all-jobs?team=Engineering%2CIT%2CSecurity%2CSite%20Reliability%20Engineering&amp;location=&amp;search=</t>
+        </is>
+      </c>
+      <c r="G176" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Engineering'</t>
+        </is>
+      </c>
+      <c r="H176" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="B177" s="1" t="inlineStr">
+        <is>
+          <t>Browse all engineering roles</t>
+        </is>
+      </c>
+      <c r="C177" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D177" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F177" s="8" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/all-jobs?team=Engineering&amp;location=&amp;search=</t>
+        </is>
+      </c>
+      <c r="G177" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Browse all engineering roles'</t>
+        </is>
+      </c>
+      <c r="H177" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="B178" s="1" t="inlineStr">
+        <is>
+          <t>student and internship opportunities</t>
+        </is>
+      </c>
+      <c r="C178" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D178" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F178" s="8" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/earlycareers</t>
+        </is>
+      </c>
+      <c r="G178" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'student and internship opportunities'</t>
+        </is>
+      </c>
+      <c r="H178" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>Builtin</t>
+        </is>
+      </c>
+      <c r="B179" s="1" t="inlineStr">
+        <is>
+          <t>Staff Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="C179" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D179" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F179" s="8" t="inlineStr">
+        <is>
+          <t>https://builtin.com/job/staff-software-development-engineer/11363675</t>
+        </is>
+      </c>
+      <c r="G179" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Staff Software Development Engineer'</t>
+        </is>
+      </c>
+      <c r="H179" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>Builtin</t>
+        </is>
+      </c>
+      <c r="B180" s="1" t="inlineStr">
+        <is>
+          <t>Staff Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="C180" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D180" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F180" s="8" t="inlineStr">
+        <is>
+          <t>https://builtin.com/job/staff-software-development-engineer/11363661</t>
+        </is>
+      </c>
+      <c r="G180" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Staff Software Development Engineer'</t>
+        </is>
+      </c>
+      <c r="H180" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>Builtin</t>
+        </is>
+      </c>
+      <c r="B181" s="1" t="inlineStr">
+        <is>
+          <t>Intern Masters Mech Eng</t>
+        </is>
+      </c>
+      <c r="C181" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D181" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F181" s="8" t="inlineStr">
+        <is>
+          <t>https://builtin.com/job/intern-masters-mech-eng/11348210</t>
+        </is>
+      </c>
+      <c r="G181" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Intern Masters Mech Eng'</t>
+        </is>
+      </c>
+      <c r="H181" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>Jobs</t>
+        </is>
+      </c>
+      <c r="B182" s="1" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="C182" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D182" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F182" s="8" t="inlineStr">
+        <is>
+          <t>https://jobs.atos.net/job/Pune-Senior-Data-Scientist-IT-Operations-&amp;-Analytics/1370842733/</t>
+        </is>
+      </c>
+      <c r="G182" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Senior Data Scientist'</t>
+        </is>
+      </c>
+      <c r="H182" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>Jobs</t>
+        </is>
+      </c>
+      <c r="B183" s="1" t="inlineStr">
+        <is>
+          <t>CRM Engineer</t>
+        </is>
+      </c>
+      <c r="C183" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D183" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F183" s="8" t="inlineStr">
+        <is>
+          <t>https://jobs.atos.net/job/Pune-CRM-Engineer-ServiceNow-%28Global-role%29/1409482933/</t>
+        </is>
+      </c>
+      <c r="G183" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'CRM Engineer'</t>
+        </is>
+      </c>
+      <c r="H183" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="B184" s="1" t="inlineStr">
+        <is>
+          <t>Living Our PurposeWe drive innovation that makes the world h</t>
+        </is>
+      </c>
+      <c r="C184" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D184" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F184" s="8" t="inlineStr">
+        <is>
+          <t>https://www.emerson.com/en/corporate/about-us/living-our-purpose</t>
+        </is>
+      </c>
+      <c r="G184" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Living Our PurposeWe drive innovation that makes the world h'</t>
+        </is>
+      </c>
+      <c r="H184" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>Acceldata</t>
+        </is>
+      </c>
+      <c r="B185" s="1" t="inlineStr">
+        <is>
+          <t>AI PipelinesDesign and run autonomous HITL workflows orchest</t>
+        </is>
+      </c>
+      <c r="C185" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D185" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F185" s="8" t="inlineStr">
+        <is>
+          <t>https://www.acceldata.io/capabilities/ai-pipelines</t>
+        </is>
+      </c>
+      <c r="G185" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'AI PipelinesDesign and run autonomous HITL workflows orchest'</t>
+        </is>
+      </c>
+      <c r="H185" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>Zenoti</t>
+        </is>
+      </c>
+      <c r="B186" s="1" t="inlineStr">
+        <is>
+          <t>AI Lead Management</t>
+        </is>
+      </c>
+      <c r="C186" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D186" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F186" s="8" t="inlineStr">
+        <is>
+          <t>https://www.zenoti.com/platform/ai-lead-management</t>
+        </is>
+      </c>
+      <c r="G186" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'AI Lead Management'</t>
+        </is>
+      </c>
+      <c r="H186" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>Leena AI</t>
+        </is>
+      </c>
+      <c r="B187" s="1" t="inlineStr">
+        <is>
+          <t>Agentic AI Architecture Overview</t>
+        </is>
+      </c>
+      <c r="C187" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D187" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F187" s="8" t="inlineStr">
+        <is>
+          <t>https://leena.ai/agentic-ai-architecture</t>
+        </is>
+      </c>
+      <c r="G187" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Agentic AI Architecture Overview'</t>
+        </is>
+      </c>
+      <c r="H187" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>Atlan</t>
+        </is>
+      </c>
+      <c r="B188" s="1" t="inlineStr">
+        <is>
+          <t>See roles that match these traits</t>
+        </is>
+      </c>
+      <c r="C188" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D188" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F188" s="8" t="inlineStr">
+        <is>
+          <t>https://atlan.com/careers/#job-list</t>
+        </is>
+      </c>
+      <c r="G188" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'See roles that match these traits'</t>
+        </is>
+      </c>
+      <c r="H188" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>Ycombinator</t>
+        </is>
+      </c>
+      <c r="B189" s="1" t="inlineStr">
+        <is>
+          <t>Quality &amp; Training Lead</t>
+        </is>
+      </c>
+      <c r="C189" s="1" t="inlineStr">
+        <is>
+          <t>Pune / Hyderabad / Bangalore</t>
+        </is>
+      </c>
+      <c r="D189" s="1" t="inlineStr">
+        <is>
+          <t>0-1 years</t>
+        </is>
+      </c>
+      <c r="F189" s="8" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/companies/clinikally/jobs/Q1M5Iaj-quality-training-lead-customer-delight</t>
+        </is>
+      </c>
+      <c r="G189" s="1" t="inlineStr">
+        <is>
+          <t>Role not in target list: 'Quality &amp; Training Lead'</t>
+        </is>
+      </c>
+      <c r="H189" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33713,6 +36354,72 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" location="job-list" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" location="/storefront/taxonomy?categoryId=31&amp;level1Name=IOT&amp;level2Name=" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" location="ai-builders" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" location="job-list" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId188"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
